--- a/data/Oct/THÁNG 10.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Oct/THÁNG 10.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3C0043-5ECB-434F-BA68-562804DBC5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405C3DF9-DA24-4E8C-9B90-4B2A2728797B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-10" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="3-10" sheetId="6" r:id="rId3"/>
     <sheet name="5-10" sheetId="7" r:id="rId4"/>
     <sheet name="6-10" sheetId="8" r:id="rId5"/>
+    <sheet name="7-10" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-10'!$A$2:$P$51</definedName>
@@ -25,6 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3-10'!$A$2:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'5-10'!$A$2:$P$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'6-10'!$A$2:$P$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'7-10'!$A$2:$P$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="892">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -2396,6 +2398,333 @@
   </si>
   <si>
     <t>kh ck shop 815k</t>
+  </si>
+  <si>
+    <t>T4.7.10.2026</t>
+  </si>
+  <si>
+    <t>THU 4</t>
+  </si>
+  <si>
+    <t>NGAY 7-10</t>
+  </si>
+  <si>
+    <t>T3.6.10.2026</t>
+  </si>
+  <si>
+    <t>Tú Oanh - fb Không Nói Xâm</t>
+  </si>
+  <si>
+    <t>HD064593</t>
+  </si>
+  <si>
+    <t>69 Dương Đình Nghệ P8</t>
+  </si>
+  <si>
+    <t>AT 07-10</t>
+  </si>
+  <si>
+    <t>07-10-2026</t>
+  </si>
+  <si>
+    <t>mỹ huyền</t>
+  </si>
+  <si>
+    <t>HD064774</t>
+  </si>
+  <si>
+    <t>hẻm 2581/27 ấp4 đường huỳnh tấn phát, xã phú xuân</t>
+  </si>
+  <si>
+    <t>Sang - fb Ivy Thụy Pham sale</t>
+  </si>
+  <si>
+    <t>HD064668</t>
+  </si>
+  <si>
+    <t>349/175 Lê Đại Hành Phường Phú Thọ</t>
+  </si>
+  <si>
+    <t>Sea</t>
+  </si>
+  <si>
+    <t>HD064748</t>
+  </si>
+  <si>
+    <t>32/16a đường số 6, P. BHHA</t>
+  </si>
+  <si>
+    <t>Vũ Hồng Ly</t>
+  </si>
+  <si>
+    <t>HD064734</t>
+  </si>
+  <si>
+    <t>240/29, Hiệp Thành 13, P Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Cin Vo</t>
+  </si>
+  <si>
+    <t>HD064606</t>
+  </si>
+  <si>
+    <t>268 bà hom p14</t>
+  </si>
+  <si>
+    <t>Bông Bông</t>
+  </si>
+  <si>
+    <t>HD064666</t>
+  </si>
+  <si>
+    <t>Saicon riverside complex (block C1) Số 4 đào trí phú thuận</t>
+  </si>
+  <si>
+    <t>Ngọc Ngân</t>
+  </si>
+  <si>
+    <t>HD064793</t>
+  </si>
+  <si>
+    <t>87 duong so 79, tan quy</t>
+  </si>
+  <si>
+    <t>Nghi</t>
+  </si>
+  <si>
+    <t>HD064749</t>
+  </si>
+  <si>
+    <t>62 Nguyễn Văn Yến, p Tân Thới Hoà</t>
+  </si>
+  <si>
+    <t>Lê Thị Minh Phượng</t>
+  </si>
+  <si>
+    <t>HD064664</t>
+  </si>
+  <si>
+    <t>101/20 đường số 9 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Chau Nguyen</t>
+  </si>
+  <si>
+    <t>HD064811</t>
+  </si>
+  <si>
+    <t>2555 QL1A Phường Tân Hưng Thuận</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thuỳ Trang</t>
+  </si>
+  <si>
+    <t>HD064608</t>
+  </si>
+  <si>
+    <t>41A Huỳnh Tịnh của p19</t>
+  </si>
+  <si>
+    <t>BN6352</t>
+  </si>
+  <si>
+    <t>HD064708</t>
+  </si>
+  <si>
+    <t>Đinh Thị Thu Hà</t>
+  </si>
+  <si>
+    <t>HD064612</t>
+  </si>
+  <si>
+    <t>176/1 Nguyễn Văn Thương, P. Thạnh Mỹ Tây</t>
+  </si>
+  <si>
+    <t>Doan Ngoc Anh Thu</t>
+  </si>
+  <si>
+    <t>HD064813</t>
+  </si>
+  <si>
+    <t>Chung cư homyland2, 307 Nguyễn duy trinh, bình trưng</t>
+  </si>
+  <si>
+    <t>Thu Ba DS</t>
+  </si>
+  <si>
+    <t>HD064675</t>
+  </si>
+  <si>
+    <t>395 Bùi Đình Tuý, p14</t>
+  </si>
+  <si>
+    <t>Linh Dịu Dàng</t>
+  </si>
+  <si>
+    <t>HD064810</t>
+  </si>
+  <si>
+    <t>362/22 lê đức thọ an nhơn</t>
+  </si>
+  <si>
+    <t>Huỳnh Anh</t>
+  </si>
+  <si>
+    <t>HD064778</t>
+  </si>
+  <si>
+    <t>Angelica Lumiere, Vinhome Grand Park, Phường long bình</t>
+  </si>
+  <si>
+    <t>Chip Chip</t>
+  </si>
+  <si>
+    <t>HD064771</t>
+  </si>
+  <si>
+    <t>71/16 thới an 16</t>
+  </si>
+  <si>
+    <t>sldraalvinaa_</t>
+  </si>
+  <si>
+    <t>HD064502</t>
+  </si>
+  <si>
+    <t>1 Đường Số 15 Villa 01 David, An Khánh</t>
+  </si>
+  <si>
+    <t>MINZZY</t>
+  </si>
+  <si>
+    <t>XE TOÀN THẮNG VỀ CÀ PHÊ PHONG LONG THÀNH ĐỒNG NAI</t>
+  </si>
+  <si>
+    <t>HOANG ANH</t>
+  </si>
+  <si>
+    <t>385/4 quang trung p go vap</t>
+  </si>
+  <si>
+    <t>vi hồ</t>
+  </si>
+  <si>
+    <t>Nhà xe Minh Quốc</t>
+  </si>
+  <si>
+    <t>Tu Tu</t>
+  </si>
+  <si>
+    <t>HD064689</t>
+  </si>
+  <si>
+    <t>466/39 le van sy f 14</t>
+  </si>
+  <si>
+    <t>Ngọc Ánh</t>
+  </si>
+  <si>
+    <t>HD064642</t>
+  </si>
+  <si>
+    <t>2/21 phan thúc duyện</t>
+  </si>
+  <si>
+    <t>HD064640</t>
+  </si>
+  <si>
+    <t>Nhi Nguyễn</t>
+  </si>
+  <si>
+    <t>HD064789</t>
+  </si>
+  <si>
+    <t>128 Hồng Hà, Phường 9</t>
+  </si>
+  <si>
+    <t>chị Thu Dương</t>
+  </si>
+  <si>
+    <t>HD064786</t>
+  </si>
+  <si>
+    <t>158 đào duy anh, P. đức nhuận</t>
+  </si>
+  <si>
+    <t>Kelly Phan</t>
+  </si>
+  <si>
+    <t>HD064673</t>
+  </si>
+  <si>
+    <t>240/6A lê thánh tôn bến thành</t>
+  </si>
+  <si>
+    <t>Trần Thu Hường</t>
+  </si>
+  <si>
+    <t>HD064655</t>
+  </si>
+  <si>
+    <t>124/28 nguyễn văn cừ, p.cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Thu Pham</t>
+  </si>
+  <si>
+    <t>HD064657</t>
+  </si>
+  <si>
+    <t>chung cư Terra Royal 280 nam kỳ khởi nghĩa, phường võ thị sáu</t>
+  </si>
+  <si>
+    <t>HD064688</t>
+  </si>
+  <si>
+    <t>My My</t>
+  </si>
+  <si>
+    <t>HD064651</t>
+  </si>
+  <si>
+    <t>CC TOPAZ ELITE PHOENIX 1A</t>
+  </si>
+  <si>
+    <t>Trang Nguyen</t>
+  </si>
+  <si>
+    <t>HD064597</t>
+  </si>
+  <si>
+    <t>Bệnh viện 1A - lý thường kiệt</t>
+  </si>
+  <si>
+    <t>Kim Chúc</t>
+  </si>
+  <si>
+    <t>HD064725</t>
+  </si>
+  <si>
+    <t>Hẻm 18B/73 Nguyễn thị minh khai đakao</t>
+  </si>
+  <si>
+    <t>Chi Linh</t>
+  </si>
+  <si>
+    <t>HD064709</t>
+  </si>
+  <si>
+    <t>813 Trần Xuân Soạn</t>
+  </si>
+  <si>
+    <t>Tranie Phan</t>
+  </si>
+  <si>
+    <t>HD064600</t>
+  </si>
+  <si>
+    <t>1041/19/7 Trần Xuân Soạn</t>
   </si>
 </sst>
 </file>
@@ -15751,7 +16080,7 @@
     </row>
     <row r="51" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H51" s="4" t="s">
-        <v>437</v>
+        <v>786</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>15</v>
@@ -16026,4 +16355,1926 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8CDCFD0-33E1-4177-9EE7-34A364128A66}">
+  <dimension ref="A1:R53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>787</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>788</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>789</v>
+      </c>
+      <c r="F3" s="18">
+        <v>11</v>
+      </c>
+      <c r="G3" s="18">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18">
+        <v>25</v>
+      </c>
+      <c r="I3" s="18">
+        <f t="shared" ref="I3:I39" si="0">G3-H3</f>
+        <v>-25</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17">
+        <v>1</v>
+      </c>
+      <c r="R3" s="19">
+        <f>H3</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>794</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="18">
+        <v>825</v>
+      </c>
+      <c r="H4" s="18">
+        <v>35</v>
+      </c>
+      <c r="I4" s="18">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>795</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>797</v>
+      </c>
+      <c r="F5" s="18">
+        <v>11</v>
+      </c>
+      <c r="G5" s="18">
+        <v>3780</v>
+      </c>
+      <c r="H5" s="18">
+        <v>35</v>
+      </c>
+      <c r="I5" s="18">
+        <f t="shared" si="0"/>
+        <v>3745</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17">
+        <v>1</v>
+      </c>
+      <c r="R5" s="19">
+        <f>H5</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>798</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>799</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>800</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18">
+        <v>30</v>
+      </c>
+      <c r="I6" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17">
+        <v>1</v>
+      </c>
+      <c r="R6" s="19">
+        <f>H6</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>801</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>802</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>803</v>
+      </c>
+      <c r="F7" s="18">
+        <v>12</v>
+      </c>
+      <c r="G7" s="18">
+        <v>1380</v>
+      </c>
+      <c r="H7" s="18">
+        <v>30</v>
+      </c>
+      <c r="I7" s="18">
+        <f t="shared" si="0"/>
+        <v>1350</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>804</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>805</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="F8" s="18">
+        <v>6</v>
+      </c>
+      <c r="G8" s="18">
+        <v>865</v>
+      </c>
+      <c r="H8" s="18">
+        <v>25</v>
+      </c>
+      <c r="I8" s="18">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>807</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>808</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>809</v>
+      </c>
+      <c r="F9" s="18">
+        <v>7</v>
+      </c>
+      <c r="G9" s="18">
+        <v>910</v>
+      </c>
+      <c r="H9" s="18">
+        <v>30</v>
+      </c>
+      <c r="I9" s="18">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>811</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>812</v>
+      </c>
+      <c r="F10" s="18">
+        <v>7</v>
+      </c>
+      <c r="G10" s="18">
+        <v>850</v>
+      </c>
+      <c r="H10" s="18">
+        <v>30</v>
+      </c>
+      <c r="I10" s="18">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>813</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>814</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>815</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" s="18">
+        <v>915</v>
+      </c>
+      <c r="H11" s="18">
+        <v>25</v>
+      </c>
+      <c r="I11" s="18">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>817</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>818</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="18">
+        <v>1410</v>
+      </c>
+      <c r="H12" s="18">
+        <v>30</v>
+      </c>
+      <c r="I12" s="18">
+        <f t="shared" si="0"/>
+        <v>1380</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>819</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>820</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>821</v>
+      </c>
+      <c r="F13" s="18">
+        <v>12</v>
+      </c>
+      <c r="G13" s="18">
+        <v>490</v>
+      </c>
+      <c r="H13" s="18">
+        <v>30</v>
+      </c>
+      <c r="I13" s="18">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>823</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="18">
+        <v>1340</v>
+      </c>
+      <c r="H14" s="18">
+        <v>20</v>
+      </c>
+      <c r="I14" s="18">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>825</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="18">
+        <v>12</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <v>30</v>
+      </c>
+      <c r="I15" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17">
+        <v>1</v>
+      </c>
+      <c r="R15" s="19">
+        <f>H15</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="18">
+        <v>1010</v>
+      </c>
+      <c r="H16" s="18">
+        <v>20</v>
+      </c>
+      <c r="I16" s="18">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="F17" s="18">
+        <v>2</v>
+      </c>
+      <c r="G17" s="18">
+        <v>820</v>
+      </c>
+      <c r="H17" s="18">
+        <v>30</v>
+      </c>
+      <c r="I17" s="18">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>833</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>834</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18">
+        <v>20</v>
+      </c>
+      <c r="I18" s="18">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17">
+        <v>1</v>
+      </c>
+      <c r="R18" s="19">
+        <f>H18</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>836</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>837</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>838</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="18">
+        <v>1485</v>
+      </c>
+      <c r="H19" s="18">
+        <v>25</v>
+      </c>
+      <c r="I19" s="18">
+        <f t="shared" si="0"/>
+        <v>1460</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>839</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="F20" s="18">
+        <v>9</v>
+      </c>
+      <c r="G20" s="18">
+        <v>0</v>
+      </c>
+      <c r="H20" s="18">
+        <v>30</v>
+      </c>
+      <c r="I20" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17">
+        <v>1</v>
+      </c>
+      <c r="R20" s="19">
+        <f>H20</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>842</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>843</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>844</v>
+      </c>
+      <c r="F21" s="18">
+        <v>12</v>
+      </c>
+      <c r="G21" s="18">
+        <v>1710</v>
+      </c>
+      <c r="H21" s="18">
+        <v>30</v>
+      </c>
+      <c r="I21" s="18">
+        <f t="shared" si="0"/>
+        <v>1680</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>845</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>846</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>847</v>
+      </c>
+      <c r="F22" s="18">
+        <v>2</v>
+      </c>
+      <c r="G22" s="18">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18">
+        <v>30</v>
+      </c>
+      <c r="I22" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17">
+        <v>1</v>
+      </c>
+      <c r="R22" s="19">
+        <f t="shared" ref="R22:R23" si="1">H22</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>848</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17" t="s">
+        <v>849</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="18">
+        <v>0</v>
+      </c>
+      <c r="H23" s="18">
+        <v>25</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17">
+        <v>1</v>
+      </c>
+      <c r="R23" s="19">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>850</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17" t="s">
+        <v>851</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="18">
+        <v>30</v>
+      </c>
+      <c r="H24" s="18">
+        <v>30</v>
+      </c>
+      <c r="I24" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>852</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17" t="s">
+        <v>853</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G25" s="18">
+        <v>0</v>
+      </c>
+      <c r="H25" s="18">
+        <v>40</v>
+      </c>
+      <c r="I25" s="18">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17">
+        <v>1</v>
+      </c>
+      <c r="R25" s="19">
+        <f>H25</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>854</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>855</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="F26" s="18">
+        <v>3</v>
+      </c>
+      <c r="G26" s="18">
+        <v>1765</v>
+      </c>
+      <c r="H26" s="18">
+        <v>25</v>
+      </c>
+      <c r="I26" s="18">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>857</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>858</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>859</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="18">
+        <v>365</v>
+      </c>
+      <c r="H27" s="18">
+        <v>25</v>
+      </c>
+      <c r="I27" s="18">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>857</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>860</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>859</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="18">
+        <v>0</v>
+      </c>
+      <c r="H28" s="18">
+        <v>0</v>
+      </c>
+      <c r="I28" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17">
+        <v>1</v>
+      </c>
+      <c r="R28" s="19">
+        <f>H28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>861</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>862</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>863</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="G29" s="18">
+        <v>480</v>
+      </c>
+      <c r="H29" s="18">
+        <v>20</v>
+      </c>
+      <c r="I29" s="18">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>864</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>865</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>866</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="G30" s="18">
+        <v>4520</v>
+      </c>
+      <c r="H30" s="18">
+        <v>35</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="0"/>
+        <v>4485</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17">
+        <v>1</v>
+      </c>
+      <c r="R30" s="19">
+        <f>H30</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>867</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>868</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="F31" s="18">
+        <v>1</v>
+      </c>
+      <c r="G31" s="18">
+        <v>0</v>
+      </c>
+      <c r="H31" s="18">
+        <v>25</v>
+      </c>
+      <c r="I31" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17">
+        <v>1</v>
+      </c>
+      <c r="R31" s="19">
+        <f>H31</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>870</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>871</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>872</v>
+      </c>
+      <c r="F32" s="18">
+        <v>1</v>
+      </c>
+      <c r="G32" s="18">
+        <v>1015</v>
+      </c>
+      <c r="H32" s="18">
+        <v>25</v>
+      </c>
+      <c r="I32" s="18">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>874</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>875</v>
+      </c>
+      <c r="F33" s="18">
+        <v>3</v>
+      </c>
+      <c r="G33" s="18">
+        <v>1315</v>
+      </c>
+      <c r="H33" s="18">
+        <v>25</v>
+      </c>
+      <c r="I33" s="18">
+        <f t="shared" si="0"/>
+        <v>1290</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="21"/>
+      <c r="B34" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>754</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>876</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>756</v>
+      </c>
+      <c r="F34" s="22">
+        <v>3</v>
+      </c>
+      <c r="G34" s="22">
+        <v>0</v>
+      </c>
+      <c r="H34" s="22">
+        <v>25</v>
+      </c>
+      <c r="I34" s="22">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="K34" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" s="21" t="s">
+        <v>791</v>
+      </c>
+      <c r="M34" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N34" s="21"/>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21">
+        <v>1</v>
+      </c>
+      <c r="R34" s="31">
+        <f>H34</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>877</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>878</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>879</v>
+      </c>
+      <c r="F35" s="18">
+        <v>7</v>
+      </c>
+      <c r="G35" s="18">
+        <v>890</v>
+      </c>
+      <c r="H35" s="18">
+        <v>30</v>
+      </c>
+      <c r="I35" s="18">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>881</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>882</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="18">
+        <v>515</v>
+      </c>
+      <c r="H36" s="18">
+        <v>25</v>
+      </c>
+      <c r="I36" s="18">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>883</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>884</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>885</v>
+      </c>
+      <c r="F37" s="18">
+        <v>1</v>
+      </c>
+      <c r="G37" s="18">
+        <v>905</v>
+      </c>
+      <c r="H37" s="18">
+        <v>25</v>
+      </c>
+      <c r="I37" s="18">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21"/>
+      <c r="B38" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>886</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>887</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>888</v>
+      </c>
+      <c r="F38" s="22">
+        <v>7</v>
+      </c>
+      <c r="G38" s="22">
+        <v>30</v>
+      </c>
+      <c r="H38" s="22">
+        <v>30</v>
+      </c>
+      <c r="I38" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="K38" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" s="21" t="s">
+        <v>791</v>
+      </c>
+      <c r="M38" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>889</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>890</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>891</v>
+      </c>
+      <c r="F39" s="18">
+        <v>7</v>
+      </c>
+      <c r="G39" s="18">
+        <v>760</v>
+      </c>
+      <c r="H39" s="18">
+        <v>30</v>
+      </c>
+      <c r="I39" s="18">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G41" s="1">
+        <f>SUBTOTAL(9,G3:G40)</f>
+        <v>30380</v>
+      </c>
+      <c r="H41" s="1">
+        <f>SUBTOTAL(9,H3:H40)</f>
+        <v>1000</v>
+      </c>
+      <c r="I41" s="1">
+        <f>SUBTOTAL(9,I3:I40)</f>
+        <v>29380</v>
+      </c>
+      <c r="J41" s="1">
+        <f>SUBTOTAL(9,J3:J40)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
+        <f>SUBTOTAL(9,K3:K40)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <f>SUBTOTAL(9,L3:L40)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <f>SUBTOTAL(9,M3:M40)</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <f>SUBTOTAL(9,N3:N40)</f>
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <f>SUBTOTAL(9,O3:O40)</f>
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <f>SUBTOTAL(9,P3:P40)</f>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="1">
+        <f>SUBTOTAL(9,Q3:Q40)</f>
+        <v>37</v>
+      </c>
+      <c r="R41" s="1">
+        <f>SUBTOTAL(9,R3:R40)</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I42" s="26"/>
+    </row>
+    <row r="45" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="8">
+        <f>SUM(I40:I44)</f>
+        <v>29380</v>
+      </c>
+      <c r="J46" s="8">
+        <f>Q41</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H47" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="10">
+        <f>R41</f>
+        <v>350</v>
+      </c>
+      <c r="J47" s="11"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H48" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="10">
+        <f>S40</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="11"/>
+    </row>
+    <row r="49" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H49" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="10">
+        <f>T40</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H50" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="10">
+        <f>U40</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="11"/>
+    </row>
+    <row r="51" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H52" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H53" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="16">
+        <f>SUM(I46:I52)</f>
+        <v>29730</v>
+      </c>
+      <c r="J53" s="16">
+        <f>SUM(J46:J50)</f>
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P39" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P39">
+      <sortCondition ref="J2:J39"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/Oct/THÁNG 10.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Oct/THÁNG 10.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405C3DF9-DA24-4E8C-9B90-4B2A2728797B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7399A5DB-1DF5-4DA9-A5CD-855E958F6A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-10'!$A$2:$P$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3-10'!$A$2:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'5-10'!$A$2:$P$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'6-10'!$A$2:$P$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'6-10'!$A$2:$P$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'7-10'!$A$2:$P$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="896">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -2725,6 +2725,18 @@
   </si>
   <si>
     <t>1041/19/7 Trần Xuân Soạn</t>
+  </si>
+  <si>
+    <t>đơn cũ thu cod 3.10</t>
+  </si>
+  <si>
+    <t>kh ck shop 825k</t>
+  </si>
+  <si>
+    <t>kh ck shop 730k</t>
+  </si>
+  <si>
+    <t>kh ck shop 1340k</t>
   </si>
 </sst>
 </file>
@@ -2832,7 +2844,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2887,6 +2899,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2917,7 +2935,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2977,13 +2995,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13978,7 +13998,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AED422A-A9D1-4515-9F08-B7C167A4D158}">
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -14075,7 +14095,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="18">
-        <f t="shared" ref="I3:I45" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I44" si="0">G3-H3</f>
         <v>990</v>
       </c>
       <c r="J3" s="17" t="s">
@@ -14688,44 +14708,46 @@
       </c>
     </row>
     <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>704</v>
-      </c>
-      <c r="F17" s="33"/>
-      <c r="G17" s="32">
-        <v>980</v>
-      </c>
-      <c r="H17" s="32">
-        <v>0</v>
-      </c>
-      <c r="I17" s="32">
-        <f t="shared" si="0"/>
-        <v>980</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>671</v>
-      </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32" t="s">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>706</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>707</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="18">
+        <v>900</v>
+      </c>
+      <c r="H17" s="18">
+        <v>20</v>
+      </c>
+      <c r="I17" s="18">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="17" t="s">
         <v>672</v>
       </c>
-      <c r="M17" s="32" t="s">
-        <v>705</v>
-      </c>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="37">
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17">
         <v>1</v>
       </c>
     </row>
@@ -14735,22 +14757,22 @@
         <v>27</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>706</v>
+        <v>527</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>708</v>
+        <v>529</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="G18" s="18">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="H18" s="18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I18" s="18">
         <f t="shared" si="0"/>
@@ -14779,26 +14801,26 @@
         <v>27</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>527</v>
+        <v>710</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>529</v>
+        <v>712</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G19" s="18">
-        <v>910</v>
+        <v>1015</v>
       </c>
       <c r="H19" s="18">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I19" s="18">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>990</v>
       </c>
       <c r="J19" s="17" t="s">
         <v>32</v>
@@ -14823,26 +14845,26 @@
         <v>27</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="G20" s="18">
-        <v>1015</v>
+        <v>1265</v>
       </c>
       <c r="H20" s="18">
         <v>25</v>
       </c>
       <c r="I20" s="18">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1240</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>32</v>
@@ -14867,26 +14889,26 @@
         <v>27</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>715</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>130</v>
+        <v>718</v>
+      </c>
+      <c r="F21" s="18">
+        <v>2</v>
       </c>
       <c r="G21" s="18">
-        <v>1265</v>
+        <v>1020</v>
       </c>
       <c r="H21" s="18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I21" s="18">
         <f t="shared" si="0"/>
-        <v>1240</v>
+        <v>990</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>32</v>
@@ -14904,6 +14926,10 @@
       <c r="Q21" s="17">
         <v>1</v>
       </c>
+      <c r="R21" s="19">
+        <f>H21</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -14911,26 +14937,26 @@
         <v>27</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="F22" s="18">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G22" s="18">
-        <v>1020</v>
+        <v>0</v>
       </c>
       <c r="H22" s="18">
         <v>30</v>
       </c>
       <c r="I22" s="18">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>-30</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>32</v>
@@ -14948,10 +14974,6 @@
       <c r="Q22" s="17">
         <v>1</v>
       </c>
-      <c r="R22" s="19">
-        <f>H22</f>
-        <v>30</v>
-      </c>
     </row>
     <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
@@ -14959,26 +14981,26 @@
         <v>27</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>721</v>
-      </c>
-      <c r="F23" s="18">
-        <v>9</v>
+        <v>724</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="G23" s="18">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="H23" s="18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I23" s="18">
         <f t="shared" si="0"/>
-        <v>-30</v>
+        <v>840</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>32</v>
@@ -15003,26 +15025,26 @@
         <v>27</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="G24" s="18">
-        <v>860</v>
+        <v>25</v>
       </c>
       <c r="H24" s="18">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I24" s="18">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>32</v>
@@ -15047,26 +15069,26 @@
         <v>27</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="F25" s="17" t="s">
         <v>77</v>
       </c>
       <c r="G25" s="18">
-        <v>25</v>
+        <v>1015</v>
       </c>
       <c r="H25" s="18">
         <v>25</v>
       </c>
       <c r="I25" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>32</v>
@@ -15084,6 +15106,10 @@
       <c r="Q25" s="17">
         <v>1</v>
       </c>
+      <c r="R25" s="19">
+        <f>H25</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="17"/>
@@ -15091,26 +15117,26 @@
         <v>27</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>728</v>
+        <v>254</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>730</v>
+        <v>256</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>77</v>
       </c>
       <c r="G26" s="18">
-        <v>1015</v>
+        <v>0</v>
       </c>
       <c r="H26" s="18">
         <v>25</v>
       </c>
       <c r="I26" s="18">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>-25</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>32</v>
@@ -15128,10 +15154,6 @@
       <c r="Q26" s="17">
         <v>1</v>
       </c>
-      <c r="R26" s="19">
-        <f>H26</f>
-        <v>25</v>
-      </c>
     </row>
     <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
@@ -15139,26 +15161,26 @@
         <v>27</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>254</v>
+        <v>732</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>256</v>
+        <v>734</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G27" s="18">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="H27" s="18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I27" s="18">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>840</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>32</v>
@@ -15176,33 +15198,37 @@
       <c r="Q27" s="17">
         <v>1</v>
       </c>
+      <c r="R27" s="19">
+        <f t="shared" ref="R27:R28" si="1">H27</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
+      <c r="A28" s="17" t="s">
+        <v>26</v>
+      </c>
       <c r="B28" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>732</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>733</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="D28" s="17"/>
       <c r="E28" s="17" t="s">
-        <v>734</v>
+        <v>180</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="G28" s="18">
-        <v>870</v>
+        <v>0</v>
       </c>
       <c r="H28" s="18">
         <v>30</v>
       </c>
       <c r="I28" s="18">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>-30</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>32</v>
@@ -15221,7 +15247,7 @@
         <v>1</v>
       </c>
       <c r="R28" s="19">
-        <f t="shared" ref="R28:R29" si="1">H28</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
@@ -15233,14 +15259,14 @@
         <v>27</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>179</v>
+        <v>293</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17" t="s">
-        <v>180</v>
+        <v>294</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="G29" s="18">
         <v>0</v>
@@ -15268,10 +15294,6 @@
       <c r="Q29" s="17">
         <v>1</v>
       </c>
-      <c r="R29" s="19">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
     </row>
     <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
@@ -15281,24 +15303,24 @@
         <v>27</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>293</v>
+        <v>735</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>77</v>
+        <v>736</v>
+      </c>
+      <c r="F30" s="18">
+        <v>9</v>
       </c>
       <c r="G30" s="18">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="H30" s="18">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I30" s="18">
         <f t="shared" si="0"/>
-        <v>-30</v>
+        <v>890</v>
       </c>
       <c r="J30" s="17" t="s">
         <v>32</v>
@@ -15325,24 +15347,24 @@
         <v>27</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17" t="s">
-        <v>736</v>
-      </c>
-      <c r="F31" s="18">
-        <v>9</v>
+        <v>738</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="G31" s="18">
-        <v>925</v>
+        <v>30</v>
       </c>
       <c r="H31" s="18">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I31" s="18">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>32</v>
@@ -15360,6 +15382,10 @@
       <c r="Q31" s="17">
         <v>1</v>
       </c>
+      <c r="R31" s="19">
+        <f>H31</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
@@ -15369,24 +15395,24 @@
         <v>27</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>130</v>
+        <v>740</v>
+      </c>
+      <c r="F32" s="18">
+        <v>12</v>
       </c>
       <c r="G32" s="18">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H32" s="18">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I32" s="18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>32</v>
@@ -15404,40 +15430,36 @@
       <c r="Q32" s="17">
         <v>1</v>
       </c>
-      <c r="R32" s="19">
-        <f>H32</f>
-        <v>30</v>
-      </c>
     </row>
     <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
-        <v>26</v>
-      </c>
+      <c r="A33" s="17"/>
       <c r="B33" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>739</v>
-      </c>
-      <c r="D33" s="17"/>
+        <v>741</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>742</v>
+      </c>
       <c r="E33" s="17" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="F33" s="18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G33" s="18">
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="H33" s="18">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I33" s="18">
         <f t="shared" si="0"/>
-        <v>-35</v>
+        <v>830</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="K33" s="17" t="s">
         <v>32</v>
@@ -15452,6 +15474,10 @@
       <c r="Q33" s="17">
         <v>1</v>
       </c>
+      <c r="R33" s="19">
+        <f>H33</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
@@ -15459,26 +15485,26 @@
         <v>27</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="F34" s="18">
         <v>1</v>
       </c>
       <c r="G34" s="18">
-        <v>855</v>
+        <v>0</v>
       </c>
       <c r="H34" s="18">
         <v>25</v>
       </c>
       <c r="I34" s="18">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>-25</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>140</v>
@@ -15496,10 +15522,6 @@
       <c r="Q34" s="17">
         <v>1</v>
       </c>
-      <c r="R34" s="19">
-        <f>H34</f>
-        <v>25</v>
-      </c>
     </row>
     <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
@@ -15507,26 +15529,26 @@
         <v>27</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>746</v>
-      </c>
-      <c r="F35" s="18">
-        <v>1</v>
+        <v>749</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="G35" s="18">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="H35" s="18">
         <v>25</v>
       </c>
       <c r="I35" s="18">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>790</v>
       </c>
       <c r="J35" s="17" t="s">
         <v>140</v>
@@ -15544,6 +15566,10 @@
       <c r="Q35" s="17">
         <v>1</v>
       </c>
+      <c r="R35" s="19">
+        <f>H35</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
@@ -15551,26 +15577,26 @@
         <v>27</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>749</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>130</v>
+        <v>752</v>
+      </c>
+      <c r="F36" s="18">
+        <v>10</v>
       </c>
       <c r="G36" s="18">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="H36" s="18">
         <v>25</v>
       </c>
       <c r="I36" s="18">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>-25</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>140</v>
@@ -15581,7 +15607,9 @@
       <c r="L36" s="17" t="s">
         <v>672</v>
       </c>
-      <c r="M36" s="17"/>
+      <c r="M36" s="20" t="s">
+        <v>753</v>
+      </c>
       <c r="N36" s="17"/>
       <c r="O36" s="17"/>
       <c r="P36" s="17"/>
@@ -15599,26 +15627,26 @@
         <v>27</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F37" s="18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G37" s="18">
-        <v>0</v>
+        <v>865</v>
       </c>
       <c r="H37" s="18">
         <v>25</v>
       </c>
       <c r="I37" s="18">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>840</v>
       </c>
       <c r="J37" s="17" t="s">
         <v>140</v>
@@ -15629,19 +15657,13 @@
       <c r="L37" s="17" t="s">
         <v>672</v>
       </c>
-      <c r="M37" s="20" t="s">
-        <v>753</v>
-      </c>
+      <c r="M37" s="17"/>
       <c r="N37" s="17"/>
       <c r="O37" s="17"/>
       <c r="P37" s="17"/>
       <c r="Q37" s="17">
         <v>1</v>
       </c>
-      <c r="R37" s="19">
-        <f>H37</f>
-        <v>25</v>
-      </c>
     </row>
     <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
@@ -15649,26 +15671,26 @@
         <v>27</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>756</v>
-      </c>
-      <c r="F38" s="18">
-        <v>3</v>
+        <v>759</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="G38" s="18">
-        <v>865</v>
+        <v>945</v>
       </c>
       <c r="H38" s="18">
         <v>25</v>
       </c>
       <c r="I38" s="18">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>920</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>140</v>
@@ -15686,6 +15708,10 @@
       <c r="Q38" s="17">
         <v>1</v>
       </c>
+      <c r="R38" s="19">
+        <f t="shared" ref="R38:R39" si="2">H38</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17"/>
@@ -15693,26 +15719,26 @@
         <v>27</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>130</v>
       </c>
       <c r="G39" s="18">
-        <v>945</v>
+        <v>0</v>
       </c>
       <c r="H39" s="18">
         <v>25</v>
       </c>
       <c r="I39" s="18">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>-25</v>
       </c>
       <c r="J39" s="17" t="s">
         <v>140</v>
@@ -15731,7 +15757,7 @@
         <v>1</v>
       </c>
       <c r="R39" s="19">
-        <f t="shared" ref="R39:R40" si="2">H39</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
     </row>
@@ -15741,16 +15767,16 @@
         <v>27</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>762</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>130</v>
+        <v>765</v>
+      </c>
+      <c r="F40" s="18">
+        <v>5</v>
       </c>
       <c r="G40" s="18">
         <v>0</v>
@@ -15778,10 +15804,6 @@
       <c r="Q40" s="17">
         <v>1</v>
       </c>
-      <c r="R40" s="19">
-        <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
     </row>
     <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17"/>
@@ -15789,26 +15811,26 @@
         <v>27</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>765</v>
-      </c>
-      <c r="F41" s="18">
-        <v>5</v>
+        <v>768</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="G41" s="18">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="H41" s="18">
         <v>25</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>890</v>
       </c>
       <c r="J41" s="17" t="s">
         <v>140</v>
@@ -15833,26 +15855,26 @@
         <v>27</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>768</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>130</v>
+        <v>771</v>
+      </c>
+      <c r="F42" s="18">
+        <v>5</v>
       </c>
       <c r="G42" s="18">
-        <v>915</v>
+        <v>1345</v>
       </c>
       <c r="H42" s="18">
         <v>25</v>
       </c>
       <c r="I42" s="18">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>1320</v>
       </c>
       <c r="J42" s="17" t="s">
         <v>140</v>
@@ -15870,33 +15892,37 @@
       <c r="Q42" s="17">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R42" s="19">
+        <f>H42</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
       <c r="B43" s="17" t="s">
         <v>27</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="F43" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G43" s="18">
-        <v>1345</v>
+        <v>0</v>
       </c>
       <c r="H43" s="18">
         <v>25</v>
       </c>
       <c r="I43" s="18">
         <f t="shared" si="0"/>
-        <v>1320</v>
+        <v>-25</v>
       </c>
       <c r="J43" s="17" t="s">
         <v>140</v>
@@ -15911,267 +15937,266 @@
       <c r="N43" s="17"/>
       <c r="O43" s="17"/>
       <c r="P43" s="17"/>
-      <c r="Q43" s="17">
-        <v>1</v>
-      </c>
-      <c r="R43" s="19">
-        <f>H43</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>772</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>773</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>774</v>
-      </c>
-      <c r="F44" s="18">
-        <v>1</v>
-      </c>
-      <c r="G44" s="18">
-        <v>0</v>
-      </c>
-      <c r="H44" s="18">
-        <v>25</v>
-      </c>
-      <c r="I44" s="18">
-        <f t="shared" si="0"/>
-        <v>-25</v>
-      </c>
-      <c r="J44" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="K44" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="L44" s="17" t="s">
+      <c r="Q43" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" s="41" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="37"/>
+      <c r="B44" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>775</v>
+      </c>
+      <c r="D44" s="37" t="s">
+        <v>776</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>777</v>
+      </c>
+      <c r="F44" s="38">
+        <v>1</v>
+      </c>
+      <c r="G44" s="38">
+        <v>0</v>
+      </c>
+      <c r="H44" s="38">
+        <v>40</v>
+      </c>
+      <c r="I44" s="38">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" s="37" t="s">
         <v>672</v>
       </c>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="38"/>
-      <c r="B45" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>775</v>
-      </c>
-      <c r="D45" s="38" t="s">
-        <v>776</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>777</v>
-      </c>
-      <c r="F45" s="39">
-        <v>1</v>
-      </c>
-      <c r="G45" s="39">
-        <v>0</v>
-      </c>
-      <c r="H45" s="39">
+      <c r="M44" s="42" t="s">
+        <v>781</v>
+      </c>
+      <c r="N44" s="37"/>
+      <c r="O44" s="37"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="39">
+        <v>1</v>
+      </c>
+      <c r="R44" s="40">
+        <f>H44</f>
         <v>40</v>
       </c>
-      <c r="I45" s="39">
-        <f t="shared" si="0"/>
-        <v>-40</v>
-      </c>
-      <c r="J45" s="38"/>
-      <c r="K45" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="L45" s="38" t="s">
-        <v>672</v>
-      </c>
-      <c r="M45" s="43" t="s">
-        <v>781</v>
-      </c>
-      <c r="N45" s="38"/>
-      <c r="O45" s="38"/>
-      <c r="P45" s="38"/>
-      <c r="Q45" s="40">
-        <v>1</v>
-      </c>
-      <c r="R45" s="41">
-        <f>H45</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="G47" s="1">
-        <f t="shared" ref="G47:R47" si="3">SUBTOTAL(9,G3:G46)</f>
-        <v>27280</v>
-      </c>
-      <c r="H47" s="1">
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G46" s="1">
+        <f t="shared" ref="G46:R46" si="3">SUBTOTAL(9,G3:G45)</f>
+        <v>26300</v>
+      </c>
+      <c r="H46" s="1">
         <f t="shared" si="3"/>
         <v>1150</v>
       </c>
-      <c r="I47" s="1">
+      <c r="I46" s="1">
         <f t="shared" si="3"/>
-        <v>26130</v>
-      </c>
-      <c r="J47" s="1">
+        <v>25150</v>
+      </c>
+      <c r="J46" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K46" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L46" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M46" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N47" s="1">
+      <c r="N46" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O47" s="1">
+      <c r="O46" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P47" s="1">
+      <c r="P46" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q47" s="1">
+      <c r="Q46" s="1">
         <f t="shared" si="3"/>
-        <v>43</v>
-      </c>
-      <c r="R47" s="1">
+        <v>42</v>
+      </c>
+      <c r="R46" s="1">
         <f t="shared" si="3"/>
         <v>420</v>
       </c>
     </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I47" s="26">
+        <f>-H63</f>
+        <v>-1680</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I48" s="26">
-        <f>-H64</f>
-        <v>-1680</v>
+      <c r="I48" s="1">
+        <v>-815</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>780</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I49" s="1">
-        <v>-815</v>
+        <v>980</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H51" s="4" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H50" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="I51" s="5" t="s">
+      <c r="I50" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J50" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H52" s="7" t="s">
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I52" s="8">
-        <f>SUM(I46:I50)</f>
+      <c r="I51" s="8">
+        <f>SUM(I45:I49)</f>
         <v>23635</v>
       </c>
-      <c r="J52" s="8">
-        <f>Q47</f>
-        <v>43</v>
-      </c>
+      <c r="J51" s="8">
+        <f>Q46</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H52" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="10">
+        <f>R46</f>
+        <v>420</v>
+      </c>
+      <c r="J52" s="11"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H53" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I53" s="10">
-        <f>R47</f>
-        <v>420</v>
+        <f>S45</f>
+        <v>0</v>
       </c>
       <c r="J53" s="11"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H54" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I54" s="10">
-        <f>S46</f>
+        <f>T45</f>
         <v>0</v>
       </c>
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H55" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I55" s="10">
-        <f>T46</f>
+        <f>U45</f>
         <v>0</v>
       </c>
       <c r="J55" s="11"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H56" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I56" s="10">
-        <f>U46</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="11"/>
+    <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H56" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H57" s="12" t="s">
-        <v>22</v>
+      <c r="H57" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
     </row>
-    <row r="58" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H58" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-    </row>
-    <row r="59" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H59" s="15" t="s">
+    <row r="58" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H58" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I59" s="16">
-        <f>SUM(I52:I58)</f>
+      <c r="I58" s="16">
+        <f>SUM(I51:I57)</f>
         <v>24055</v>
       </c>
-      <c r="J59" s="16">
-        <f>SUM(J52:J56)</f>
-        <v>43</v>
+      <c r="J58" s="16">
+        <f>SUM(J51:J55)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>184</v>
+      <c r="A61" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>775</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>776</v>
+      </c>
+      <c r="D61" s="24" t="s">
+        <v>777</v>
+      </c>
+      <c r="E61" s="25">
+        <v>1</v>
+      </c>
+      <c r="F61" s="25">
+        <v>0</v>
+      </c>
+      <c r="G61" s="25">
+        <v>0</v>
+      </c>
+      <c r="H61" s="25">
+        <f>F61-G61</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J61" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K61" s="24" t="s">
+        <v>672</v>
+      </c>
+      <c r="L61" s="24" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -16179,26 +16204,26 @@
         <v>27</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>775</v>
+        <v>630</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>776</v>
+        <v>631</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>777</v>
+        <v>632</v>
       </c>
       <c r="E62" s="25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="25">
-        <v>0</v>
+        <v>1705</v>
       </c>
       <c r="G62" s="25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H62" s="25">
         <f>F62-G62</f>
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="I62" s="24" t="s">
         <v>188</v>
@@ -16207,149 +16232,150 @@
         <v>32</v>
       </c>
       <c r="K62" s="24" t="s">
+        <v>442</v>
+      </c>
+      <c r="L62" s="24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H63" s="26">
+        <f>SUM(H61:H62)</f>
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>633</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>634</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>635</v>
+      </c>
+      <c r="E65" s="27">
+        <v>4</v>
+      </c>
+      <c r="F65" s="27">
+        <v>815</v>
+      </c>
+      <c r="G65" s="27">
+        <v>0</v>
+      </c>
+      <c r="H65" s="27">
+        <f>F65-G65</f>
+        <v>815</v>
+      </c>
+      <c r="I65" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J65" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K65" s="27" t="s">
+        <v>442</v>
+      </c>
+      <c r="L65" s="20" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>750</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>751</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>752</v>
+      </c>
+      <c r="E67" s="35">
+        <v>10</v>
+      </c>
+      <c r="F67" s="35">
+        <v>885</v>
+      </c>
+      <c r="G67" s="35">
+        <v>0</v>
+      </c>
+      <c r="H67" s="35">
+        <f>F67-G67</f>
+        <v>885</v>
+      </c>
+      <c r="I67" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="J67" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K67" s="34" t="s">
         <v>672</v>
       </c>
-      <c r="L62" s="24" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B63" s="24" t="s">
-        <v>630</v>
-      </c>
-      <c r="C63" s="24" t="s">
-        <v>631</v>
-      </c>
-      <c r="D63" s="24" t="s">
-        <v>632</v>
-      </c>
-      <c r="E63" s="25">
-        <v>3</v>
-      </c>
-      <c r="F63" s="25">
-        <v>1705</v>
-      </c>
-      <c r="G63" s="25">
-        <v>25</v>
-      </c>
-      <c r="H63" s="25">
-        <f>F63-G63</f>
-        <v>1680</v>
-      </c>
-      <c r="I63" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="J63" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K63" s="24" t="s">
-        <v>442</v>
-      </c>
-      <c r="L63" s="24" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H64" s="26">
-        <f>SUM(H62:H63)</f>
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B66" s="27" t="s">
-        <v>633</v>
-      </c>
-      <c r="C66" s="27" t="s">
-        <v>634</v>
-      </c>
-      <c r="D66" s="27" t="s">
-        <v>635</v>
-      </c>
-      <c r="E66" s="27">
-        <v>4</v>
-      </c>
-      <c r="F66" s="27">
-        <v>815</v>
-      </c>
-      <c r="G66" s="27">
-        <v>0</v>
-      </c>
-      <c r="H66" s="27">
-        <f>F66-G66</f>
-        <v>815</v>
-      </c>
-      <c r="I66" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="J66" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="K66" s="27" t="s">
-        <v>442</v>
-      </c>
-      <c r="L66" s="20" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>779</v>
+      <c r="L67" s="20" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B68" s="34" t="s">
-        <v>750</v>
-      </c>
-      <c r="C68" s="34" t="s">
-        <v>751</v>
-      </c>
-      <c r="D68" s="34" t="s">
-        <v>752</v>
-      </c>
-      <c r="E68" s="35">
-        <v>10</v>
-      </c>
-      <c r="F68" s="35">
-        <v>885</v>
-      </c>
-      <c r="G68" s="35">
-        <v>0</v>
-      </c>
-      <c r="H68" s="35">
-        <f>F68-G68</f>
-        <v>885</v>
-      </c>
-      <c r="I68" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="J68" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="K68" s="34" t="s">
+      <c r="A68" s="1" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B69" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C69" s="32" t="s">
+        <v>365</v>
+      </c>
+      <c r="D69" s="32" t="s">
+        <v>704</v>
+      </c>
+      <c r="E69" s="33"/>
+      <c r="F69" s="32">
+        <v>980</v>
+      </c>
+      <c r="G69" s="32">
+        <v>0</v>
+      </c>
+      <c r="H69" s="32">
+        <f t="shared" ref="H69" si="4">F69-G69</f>
+        <v>980</v>
+      </c>
+      <c r="I69" s="32" t="s">
+        <v>671</v>
+      </c>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32" t="s">
         <v>672</v>
       </c>
-      <c r="L68" s="20" t="s">
-        <v>753</v>
+      <c r="L69" s="43" t="s">
+        <v>705</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P45" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P45">
-      <sortCondition ref="J2:J45"/>
+  <autoFilter ref="A2:P44" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P44">
+      <sortCondition ref="J2:J44"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16359,7 +16385,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8CDCFD0-33E1-4177-9EE7-34A364128A66}">
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -16498,14 +16524,14 @@
         <v>202</v>
       </c>
       <c r="G4" s="18">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="H4" s="18">
         <v>35</v>
       </c>
       <c r="I4" s="18">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>-35</v>
       </c>
       <c r="J4" s="17" t="s">
         <v>790</v>
@@ -16516,12 +16542,18 @@
       <c r="L4" s="17" t="s">
         <v>791</v>
       </c>
-      <c r="M4" s="17"/>
+      <c r="M4" s="44" t="s">
+        <v>893</v>
+      </c>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17">
         <v>1</v>
+      </c>
+      <c r="R4" s="19">
+        <f>H4</f>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
@@ -16948,14 +16980,14 @@
         <v>98</v>
       </c>
       <c r="G14" s="18">
-        <v>1340</v>
+        <v>0</v>
       </c>
       <c r="H14" s="18">
         <v>20</v>
       </c>
       <c r="I14" s="18">
         <f t="shared" si="0"/>
-        <v>1320</v>
+        <v>-20</v>
       </c>
       <c r="J14" s="17" t="s">
         <v>32</v>
@@ -16966,12 +16998,18 @@
       <c r="L14" s="17" t="s">
         <v>791</v>
       </c>
-      <c r="M14" s="17"/>
+      <c r="M14" s="20" t="s">
+        <v>895</v>
+      </c>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
       <c r="Q14" s="17">
         <v>1</v>
+      </c>
+      <c r="R14" s="19">
+        <f>H14</f>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
@@ -18098,14 +18136,14 @@
         <v>7</v>
       </c>
       <c r="G39" s="18">
-        <v>760</v>
+        <v>30</v>
       </c>
       <c r="H39" s="18">
         <v>30</v>
       </c>
       <c r="I39" s="18">
         <f t="shared" si="0"/>
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="J39" s="17" t="s">
         <v>140</v>
@@ -18116,7 +18154,9 @@
       <c r="L39" s="17" t="s">
         <v>791</v>
       </c>
-      <c r="M39" s="17"/>
+      <c r="M39" s="44" t="s">
+        <v>894</v>
+      </c>
       <c r="N39" s="17"/>
       <c r="O39" s="17"/>
       <c r="P39" s="17"/>
@@ -18126,52 +18166,52 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G41" s="1">
-        <f>SUBTOTAL(9,G3:G40)</f>
-        <v>30380</v>
+        <f t="shared" ref="G41:R41" si="2">SUBTOTAL(9,G3:G40)</f>
+        <v>27485</v>
       </c>
       <c r="H41" s="1">
-        <f>SUBTOTAL(9,H3:H40)</f>
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
       <c r="I41" s="1">
-        <f>SUBTOTAL(9,I3:I40)</f>
-        <v>29380</v>
+        <f t="shared" si="2"/>
+        <v>26485</v>
       </c>
       <c r="J41" s="1">
-        <f>SUBTOTAL(9,J3:J40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K41" s="1">
-        <f>SUBTOTAL(9,K3:K40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L41" s="1">
-        <f>SUBTOTAL(9,L3:L40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <f>SUBTOTAL(9,M3:M40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N41" s="1">
-        <f>SUBTOTAL(9,N3:N40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O41" s="1">
-        <f>SUBTOTAL(9,O3:O40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P41" s="1">
-        <f>SUBTOTAL(9,P3:P40)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q41" s="1">
-        <f>SUBTOTAL(9,Q3:Q40)</f>
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
       <c r="R41" s="1">
-        <f>SUBTOTAL(9,R3:R40)</f>
-        <v>350</v>
+        <f t="shared" si="2"/>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -18194,7 +18234,7 @@
       </c>
       <c r="I46" s="8">
         <f>SUM(I40:I44)</f>
-        <v>29380</v>
+        <v>26485</v>
       </c>
       <c r="J46" s="8">
         <f>Q41</f>
@@ -18207,7 +18247,7 @@
       </c>
       <c r="I47" s="10">
         <f>R41</f>
-        <v>350</v>
+        <v>405</v>
       </c>
       <c r="J47" s="11"/>
     </row>
@@ -18221,7 +18261,7 @@
       </c>
       <c r="J48" s="11"/>
     </row>
-    <row r="49" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H49" s="9" t="s">
         <v>20</v>
       </c>
@@ -18231,7 +18271,7 @@
       </c>
       <c r="J49" s="11"/>
     </row>
-    <row r="50" spans="8:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H50" s="9" t="s">
         <v>21</v>
       </c>
@@ -18241,31 +18281,114 @@
       </c>
       <c r="J50" s="11"/>
     </row>
-    <row r="51" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H51" s="12" t="s">
         <v>22</v>
       </c>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
     </row>
-    <row r="52" spans="8:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H52" s="14" t="s">
         <v>23</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
     </row>
-    <row r="53" spans="8:10" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H53" s="15" t="s">
         <v>24</v>
       </c>
       <c r="I53" s="16">
         <f>SUM(I46:I52)</f>
-        <v>29730</v>
+        <v>26890</v>
       </c>
       <c r="J53" s="16">
         <f>SUM(J46:J50)</f>
         <v>37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>792</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>793</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>794</v>
+      </c>
+      <c r="E56" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="F56" s="35">
+        <v>825</v>
+      </c>
+      <c r="G56" s="35">
+        <v>0</v>
+      </c>
+      <c r="H56" s="35">
+        <f t="shared" ref="H56:H57" si="3">F56-G56</f>
+        <v>825</v>
+      </c>
+      <c r="I56" s="34" t="s">
+        <v>790</v>
+      </c>
+      <c r="J56" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K56" s="34" t="s">
+        <v>791</v>
+      </c>
+      <c r="L56" s="44" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>889</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>890</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>891</v>
+      </c>
+      <c r="E57" s="45">
+        <v>7</v>
+      </c>
+      <c r="F57" s="45">
+        <v>730</v>
+      </c>
+      <c r="G57" s="45">
+        <v>0</v>
+      </c>
+      <c r="H57" s="45">
+        <f t="shared" si="3"/>
+        <v>730</v>
+      </c>
+      <c r="I57" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="J57" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="K57" s="27" t="s">
+        <v>791</v>
+      </c>
+      <c r="L57" s="44" t="s">
+        <v>894</v>
       </c>
     </row>
   </sheetData>

--- a/data/Oct/THÁNG 10.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Oct/THÁNG 10.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1820BBAE-AC5C-4815-B153-3404A5F0981C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8ADC85-A00B-485C-91DF-80DDAE44759A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-10" sheetId="4" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="13-10" sheetId="14" r:id="rId11"/>
     <sheet name="14-10" sheetId="15" r:id="rId12"/>
     <sheet name="15-10" sheetId="16" r:id="rId13"/>
+    <sheet name="16-10" sheetId="17" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'10-10'!$A$2:$P$32</definedName>
@@ -34,6 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'13-10'!$A$2:$P$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'14-10'!$A$2:$P$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'15-10'!$A$2:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'16-10'!$A$2:$P$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-10'!$A$2:$P$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3-10'!$A$2:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'5-10'!$A$2:$P$84</definedName>
@@ -63,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5087" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5485" uniqueCount="1749">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4974,6 +4976,342 @@
   </si>
   <si>
     <t>32 ng du. Bến nghé</t>
+  </si>
+  <si>
+    <t>NGAY 16-10</t>
+  </si>
+  <si>
+    <t>T6.16.10.2026</t>
+  </si>
+  <si>
+    <t>Milly Đỗ</t>
+  </si>
+  <si>
+    <t>HD067453</t>
+  </si>
+  <si>
+    <t>14/144/10/7 phạm hùng, bình hưng</t>
+  </si>
+  <si>
+    <t>AT 16-10</t>
+  </si>
+  <si>
+    <t>16-10-2026</t>
+  </si>
+  <si>
+    <t>Bảo Uyên</t>
+  </si>
+  <si>
+    <t>HD067329</t>
+  </si>
+  <si>
+    <t>5606a vinhome grand park ( Đ. cầu vồng, Long Bình)</t>
+  </si>
+  <si>
+    <t>Christy Lương</t>
+  </si>
+  <si>
+    <t>HD067357</t>
+  </si>
+  <si>
+    <t>1079 tạ quang bửu phường bình đông</t>
+  </si>
+  <si>
+    <t>Tran Ngọc</t>
+  </si>
+  <si>
+    <t>HD067400</t>
+  </si>
+  <si>
+    <t>449 lạc long quân phường 5</t>
+  </si>
+  <si>
+    <t>Hồng Nguyễn</t>
+  </si>
+  <si>
+    <t>HD067451</t>
+  </si>
+  <si>
+    <t>621 Tân Kỳ Tân Quý, P. Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Thao Yumi</t>
+  </si>
+  <si>
+    <t>HD067551</t>
+  </si>
+  <si>
+    <t>Số 17, Đường Số 13, Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Đinh Lily</t>
+  </si>
+  <si>
+    <t>HD067487</t>
+  </si>
+  <si>
+    <t>33C Song Hành Quốc Lộ 50, Phong Phú</t>
+  </si>
+  <si>
+    <t>Phạm Vũ Minh Hậu</t>
+  </si>
+  <si>
+    <t>HD067447</t>
+  </si>
+  <si>
+    <t>The Opera Biệt thự Valora Ik6.33 đường số 11, Lk6-33 mới đúng ạ, đường số 11, Xã Bình Hưng</t>
+  </si>
+  <si>
+    <t>Tố Như</t>
+  </si>
+  <si>
+    <t>HD067550</t>
+  </si>
+  <si>
+    <t>688/23/1C Hương Lộ 2, Phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiên Hương</t>
+  </si>
+  <si>
+    <t>HD067544</t>
+  </si>
+  <si>
+    <t>16 đường 168 Phước Long A</t>
+  </si>
+  <si>
+    <t>HD067599</t>
+  </si>
+  <si>
+    <t>38A đường 3158A phạm thế hiển phường bình đông(phuong 7) Đối diệncổng trường THPT nguyễn văn linh</t>
+  </si>
+  <si>
+    <t>KHONGKWAN</t>
+  </si>
+  <si>
+    <t>Ngõ 72 đường 18B, phường Bình Hưng Hòa A</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải ( Bow)</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Chi Nguyen</t>
+  </si>
+  <si>
+    <t>312 Lô G cư xá Thanh Đa, p. Bình Quới</t>
+  </si>
+  <si>
+    <t>.Endny/ HOANG MEO</t>
+  </si>
+  <si>
+    <t>HD067328</t>
+  </si>
+  <si>
+    <t>22, ĐƯỜNG TÂN THỚI NHẤT 1B, PHƯỜNG TÂN THỚI NHẤT</t>
+  </si>
+  <si>
+    <t>Mai Lê</t>
+  </si>
+  <si>
+    <t>HD067391</t>
+  </si>
+  <si>
+    <t>204/B12 Nguyễn văn hưởng, p thảo điền</t>
+  </si>
+  <si>
+    <t>HD067368</t>
+  </si>
+  <si>
+    <t>Thanh Thảo Sumi</t>
+  </si>
+  <si>
+    <t>HD067392</t>
+  </si>
+  <si>
+    <t>Căn 16.07 toà A2 chung cư Hoàng Anh River View, số 37 đường Nguyễn Văn Hưởng, phường An Khánh (phường cũ là Thảo Điền)</t>
+  </si>
+  <si>
+    <t>HD067598</t>
+  </si>
+  <si>
+    <t>Trần Thảo Anh</t>
+  </si>
+  <si>
+    <t>HD067567</t>
+  </si>
+  <si>
+    <t>Veronica Nhà Màu Vàng, 216/26, Nguyễn Văn Hưởng, Phường An Khánh</t>
+  </si>
+  <si>
+    <t>HD067573</t>
+  </si>
+  <si>
+    <t>Hằng Kimm</t>
+  </si>
+  <si>
+    <t>HD067330</t>
+  </si>
+  <si>
+    <t>31/3 ung văn khiêm thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>Chế Vân</t>
+  </si>
+  <si>
+    <t>HD067563</t>
+  </si>
+  <si>
+    <t>496/1/56 dương quảng hàm phường an nhơn</t>
+  </si>
+  <si>
+    <t>Vũ Thị Hà</t>
+  </si>
+  <si>
+    <t>HD067607</t>
+  </si>
+  <si>
+    <t>20 vũ tông phan</t>
+  </si>
+  <si>
+    <t>Bảo Như</t>
+  </si>
+  <si>
+    <t>HD067374</t>
+  </si>
+  <si>
+    <t>e208 nguyễn hữu cảnh p22 toà nhà landmark 3</t>
+  </si>
+  <si>
+    <t>andu dang</t>
+  </si>
+  <si>
+    <t>24/5G, Ấp Đông Lân, Xã Bà Điểm</t>
+  </si>
+  <si>
+    <t>Trân Helen</t>
+  </si>
+  <si>
+    <t>HD067483</t>
+  </si>
+  <si>
+    <t>36/15 Yên Thế, Phường Tân Sơn Hoà, Phường Tân Bình</t>
+  </si>
+  <si>
+    <t>HD067386</t>
+  </si>
+  <si>
+    <t>Saigon riverside complex (block C1) Số 4 đào trí phú thuận</t>
+  </si>
+  <si>
+    <t>Thanh Hiền</t>
+  </si>
+  <si>
+    <t>HD067569</t>
+  </si>
+  <si>
+    <t>Block D1, Chung cư Hoàng Anh Gia Lai 3, Đường Nguyễn Hữu Thọ, xã Phước Kiển</t>
+  </si>
+  <si>
+    <t>kh ck shop 1965k</t>
+  </si>
+  <si>
+    <t>Việt Trinh</t>
+  </si>
+  <si>
+    <t>HD067371</t>
+  </si>
+  <si>
+    <t>Số 42, Đường Phùng Hưng Phường Chợ Lớn</t>
+  </si>
+  <si>
+    <t>HD067377</t>
+  </si>
+  <si>
+    <t>chung cư sunrise city view block B</t>
+  </si>
+  <si>
+    <t>HD067527</t>
+  </si>
+  <si>
+    <t>156 Trần Nhân Tôn, phường Vườn Lài (phường 2)</t>
+  </si>
+  <si>
+    <t>Veriska Erica</t>
+  </si>
+  <si>
+    <t>HD067552</t>
+  </si>
+  <si>
+    <t>Lan Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD067596</t>
+  </si>
+  <si>
+    <t>96 hoàng hoa thám</t>
+  </si>
+  <si>
+    <t>THI (KT Ng)</t>
+  </si>
+  <si>
+    <t>HD067570</t>
+  </si>
+  <si>
+    <t>39 Nguyen thi Thap khu dan cu him lam phuong tan hung ( me in nail)</t>
+  </si>
+  <si>
+    <t>kh ck shop 960k</t>
+  </si>
+  <si>
+    <t>Dinh Luong</t>
+  </si>
+  <si>
+    <t>HD067500</t>
+  </si>
+  <si>
+    <t>246 nguyễn duy dương f4</t>
+  </si>
+  <si>
+    <t>Ngọc Hiền</t>
+  </si>
+  <si>
+    <t>HD067584</t>
+  </si>
+  <si>
+    <t>13c lê thánh tôn</t>
+  </si>
+  <si>
+    <t>Jessicaa</t>
+  </si>
+  <si>
+    <t>HD067352</t>
+  </si>
+  <si>
+    <t>17A Cộng Hòa, Tân Sơn Nhất</t>
+  </si>
+  <si>
+    <t>HD067601</t>
+  </si>
+  <si>
+    <t>phương uyên</t>
+  </si>
+  <si>
+    <t>290 An Dương Vương phường 4 (phường Chợ Quán mới)</t>
+  </si>
+  <si>
+    <t>Minea</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương, Phường 9</t>
+  </si>
+  <si>
+    <t>DaRaVin</t>
+  </si>
+  <si>
+    <t>301 Phạm Ngũ Lão, Phường Phạm Ngũ Lão</t>
   </si>
 </sst>
 </file>
@@ -5143,7 +5481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -5166,13 +5504,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5247,6 +5607,13 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18507,51 +18874,51 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G45" s="1">
-        <f>SUBTOTAL(9,G3:G44)</f>
+        <f t="shared" ref="G45:R45" si="4">SUBTOTAL(9,G3:G44)</f>
         <v>35265</v>
       </c>
       <c r="H45" s="1">
-        <f>SUBTOTAL(9,H3:H44)</f>
+        <f t="shared" si="4"/>
         <v>1220</v>
       </c>
       <c r="I45" s="1">
-        <f>SUBTOTAL(9,I3:I44)</f>
+        <f t="shared" si="4"/>
         <v>34045</v>
       </c>
       <c r="J45" s="1">
-        <f>SUBTOTAL(9,J3:J44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K45" s="1">
-        <f>SUBTOTAL(9,K3:K44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L45" s="1">
-        <f>SUBTOTAL(9,L3:L44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M45" s="1">
-        <f>SUBTOTAL(9,M3:M44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f>SUBTOTAL(9,N3:N44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O45" s="1">
-        <f>SUBTOTAL(9,O3:O44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P45" s="1">
-        <f>SUBTOTAL(9,P3:P44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q45" s="1">
-        <f>SUBTOTAL(9,Q3:Q44)</f>
+        <f t="shared" si="4"/>
         <v>41</v>
       </c>
       <c r="R45" s="1">
-        <f>SUBTOTAL(9,R3:R44)</f>
+        <f t="shared" si="4"/>
         <v>415</v>
       </c>
     </row>
@@ -18703,6 +19070,2468 @@
   <autoFilter ref="A2:P43" xr:uid="{00000000-0009-0000-0000-000006000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P43">
       <sortCondition ref="J2:J43"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{863EE82C-6F7E-4D0B-A618-C3DD6751B0BB}">
+  <dimension ref="A1:R65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="18">
+        <v>3850</v>
+      </c>
+      <c r="H3" s="18">
+        <v>45</v>
+      </c>
+      <c r="I3" s="18">
+        <f t="shared" ref="I3:I48" si="0">G3-H3</f>
+        <v>3805</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="52">
+        <v>1</v>
+      </c>
+      <c r="R3" s="53">
+        <f>H3</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="F4" s="18">
+        <v>9</v>
+      </c>
+      <c r="G4" s="18">
+        <v>820</v>
+      </c>
+      <c r="H4" s="18">
+        <v>30</v>
+      </c>
+      <c r="I4" s="18">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="52">
+        <v>1</v>
+      </c>
+      <c r="R4" s="54"/>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F5" s="18">
+        <v>8</v>
+      </c>
+      <c r="G5" s="18">
+        <v>950</v>
+      </c>
+      <c r="H5" s="18">
+        <v>30</v>
+      </c>
+      <c r="I5" s="18">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="52">
+        <v>1</v>
+      </c>
+      <c r="R5" s="54"/>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F6" s="18">
+        <v>11</v>
+      </c>
+      <c r="G6" s="18">
+        <v>1575</v>
+      </c>
+      <c r="H6" s="18">
+        <v>25</v>
+      </c>
+      <c r="I6" s="18">
+        <f t="shared" si="0"/>
+        <v>1550</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="52">
+        <v>1</v>
+      </c>
+      <c r="R6" s="54"/>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="18">
+        <v>790</v>
+      </c>
+      <c r="H7" s="18">
+        <v>30</v>
+      </c>
+      <c r="I7" s="18">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="52">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>1658</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="18">
+        <v>1110</v>
+      </c>
+      <c r="H8" s="18">
+        <v>30</v>
+      </c>
+      <c r="I8" s="18">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="52">
+        <v>1</v>
+      </c>
+      <c r="R8" s="54"/>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="18">
+        <v>905</v>
+      </c>
+      <c r="H9" s="18">
+        <v>35</v>
+      </c>
+      <c r="I9" s="18">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="52">
+        <v>1</v>
+      </c>
+      <c r="R9" s="54"/>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>1662</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>1664</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <v>35</v>
+      </c>
+      <c r="I10" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="52">
+        <v>1</v>
+      </c>
+      <c r="R10" s="53">
+        <f t="shared" ref="R10:R11" si="1">H10</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18">
+        <v>30</v>
+      </c>
+      <c r="I11" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="52">
+        <v>1</v>
+      </c>
+      <c r="R11" s="53">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>1668</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F12" s="18">
+        <v>9</v>
+      </c>
+      <c r="G12" s="18">
+        <v>460</v>
+      </c>
+      <c r="H12" s="18">
+        <v>30</v>
+      </c>
+      <c r="I12" s="18">
+        <f t="shared" si="0"/>
+        <v>430</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="52">
+        <v>1</v>
+      </c>
+      <c r="R12" s="54"/>
+    </row>
+    <row r="13" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F13" s="22">
+        <v>8</v>
+      </c>
+      <c r="G13" s="22">
+        <v>170</v>
+      </c>
+      <c r="H13" s="22">
+        <v>30</v>
+      </c>
+      <c r="I13" s="22">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="55">
+        <v>1</v>
+      </c>
+      <c r="R13" s="56"/>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="18">
+        <v>2140</v>
+      </c>
+      <c r="H14" s="18">
+        <v>40</v>
+      </c>
+      <c r="I14" s="18">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="52">
+        <v>1</v>
+      </c>
+      <c r="R14" s="54"/>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <v>35</v>
+      </c>
+      <c r="I15" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="52">
+        <v>1</v>
+      </c>
+      <c r="R15" s="53">
+        <f t="shared" ref="R15:R19" si="2">H15</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <v>35</v>
+      </c>
+      <c r="I16" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="52">
+        <v>1</v>
+      </c>
+      <c r="R16" s="53">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="18">
+        <v>0</v>
+      </c>
+      <c r="H17" s="18">
+        <v>35</v>
+      </c>
+      <c r="I17" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="52">
+        <v>1</v>
+      </c>
+      <c r="R17" s="53">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="22">
+        <v>0</v>
+      </c>
+      <c r="H18" s="22">
+        <v>20</v>
+      </c>
+      <c r="I18" s="22">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="55">
+        <v>1</v>
+      </c>
+      <c r="R18" s="57">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F19" s="18">
+        <v>12</v>
+      </c>
+      <c r="G19" s="18">
+        <v>0</v>
+      </c>
+      <c r="H19" s="18">
+        <v>30</v>
+      </c>
+      <c r="I19" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="52">
+        <v>1</v>
+      </c>
+      <c r="R19" s="53">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F20" s="18">
+        <v>2</v>
+      </c>
+      <c r="G20" s="18">
+        <v>1070</v>
+      </c>
+      <c r="H20" s="18">
+        <v>30</v>
+      </c>
+      <c r="I20" s="18">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="52">
+        <v>1</v>
+      </c>
+      <c r="R20" s="54"/>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="18">
+        <v>0</v>
+      </c>
+      <c r="H21" s="18">
+        <v>30</v>
+      </c>
+      <c r="I21" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="52">
+        <v>1</v>
+      </c>
+      <c r="R21" s="53">
+        <f>H21</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>1687</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F22" s="18">
+        <v>2</v>
+      </c>
+      <c r="G22" s="18">
+        <v>720</v>
+      </c>
+      <c r="H22" s="18">
+        <v>30</v>
+      </c>
+      <c r="I22" s="18">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="52">
+        <v>1</v>
+      </c>
+      <c r="R22" s="54"/>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="18">
+        <v>1210</v>
+      </c>
+      <c r="H23" s="18">
+        <v>20</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="0"/>
+        <v>1190</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="52">
+        <v>1</v>
+      </c>
+      <c r="R23" s="54"/>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F24" s="18">
+        <v>2</v>
+      </c>
+      <c r="G24" s="18">
+        <v>920</v>
+      </c>
+      <c r="H24" s="18">
+        <v>30</v>
+      </c>
+      <c r="I24" s="18">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="52">
+        <v>1</v>
+      </c>
+      <c r="R24" s="54"/>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F25" s="18">
+        <v>2</v>
+      </c>
+      <c r="G25" s="18">
+        <v>960</v>
+      </c>
+      <c r="H25" s="18">
+        <v>0</v>
+      </c>
+      <c r="I25" s="18">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="52">
+        <v>1</v>
+      </c>
+      <c r="R25" s="54"/>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>1696</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="18">
+        <v>510</v>
+      </c>
+      <c r="H26" s="18">
+        <v>20</v>
+      </c>
+      <c r="I26" s="18">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="52">
+        <v>1</v>
+      </c>
+      <c r="R26" s="54"/>
+    </row>
+    <row r="27" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="22">
+        <v>25</v>
+      </c>
+      <c r="H27" s="22">
+        <v>25</v>
+      </c>
+      <c r="I27" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="55">
+        <v>1</v>
+      </c>
+      <c r="R27" s="56"/>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>1702</v>
+      </c>
+      <c r="F28" s="18">
+        <v>2</v>
+      </c>
+      <c r="G28" s="18">
+        <v>1090</v>
+      </c>
+      <c r="H28" s="18">
+        <v>30</v>
+      </c>
+      <c r="I28" s="18">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="52">
+        <v>1</v>
+      </c>
+      <c r="R28" s="54"/>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="18">
+        <v>950</v>
+      </c>
+      <c r="H29" s="18">
+        <v>20</v>
+      </c>
+      <c r="I29" s="18">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="52">
+        <v>1</v>
+      </c>
+      <c r="R29" s="54"/>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="18">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18">
+        <v>70</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="0"/>
+        <v>-70</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="52">
+        <v>1</v>
+      </c>
+      <c r="R30" s="53">
+        <f t="shared" ref="R30:R33" si="3">H30</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="18">
+        <v>12</v>
+      </c>
+      <c r="G31" s="18">
+        <v>0</v>
+      </c>
+      <c r="H31" s="18">
+        <v>35</v>
+      </c>
+      <c r="I31" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="52">
+        <v>1</v>
+      </c>
+      <c r="R31" s="53">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>992</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="F32" s="18">
+        <v>12</v>
+      </c>
+      <c r="G32" s="18">
+        <v>0</v>
+      </c>
+      <c r="H32" s="18">
+        <v>35</v>
+      </c>
+      <c r="I32" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="52">
+        <v>1</v>
+      </c>
+      <c r="R32" s="53">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>1709</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>1710</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G33" s="18">
+        <v>0</v>
+      </c>
+      <c r="H33" s="18">
+        <v>25</v>
+      </c>
+      <c r="I33" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="52">
+        <v>1</v>
+      </c>
+      <c r="R33" s="53">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>807</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="F34" s="18">
+        <v>7</v>
+      </c>
+      <c r="G34" s="18">
+        <v>1510</v>
+      </c>
+      <c r="H34" s="18">
+        <v>30</v>
+      </c>
+      <c r="I34" s="18">
+        <f t="shared" si="0"/>
+        <v>1480</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="52">
+        <v>1</v>
+      </c>
+      <c r="R34" s="54"/>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>1715</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="G35" s="18">
+        <v>0</v>
+      </c>
+      <c r="H35" s="18">
+        <v>35</v>
+      </c>
+      <c r="I35" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M35" s="49" t="s">
+        <v>1716</v>
+      </c>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="52">
+        <v>1</v>
+      </c>
+      <c r="R35" s="53">
+        <f t="shared" ref="R35" si="4">H35</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>1719</v>
+      </c>
+      <c r="F36" s="18">
+        <v>5</v>
+      </c>
+      <c r="G36" s="18">
+        <v>785</v>
+      </c>
+      <c r="H36" s="18">
+        <v>25</v>
+      </c>
+      <c r="I36" s="18">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="52">
+        <v>1</v>
+      </c>
+      <c r="R36" s="54"/>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>1721</v>
+      </c>
+      <c r="F37" s="18">
+        <v>7</v>
+      </c>
+      <c r="G37" s="18">
+        <v>880</v>
+      </c>
+      <c r="H37" s="18">
+        <v>30</v>
+      </c>
+      <c r="I37" s="18">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="52">
+        <v>1</v>
+      </c>
+      <c r="R37" s="54"/>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F38" s="18">
+        <v>10</v>
+      </c>
+      <c r="G38" s="18">
+        <v>0</v>
+      </c>
+      <c r="H38" s="18">
+        <v>25</v>
+      </c>
+      <c r="I38" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="52">
+        <v>1</v>
+      </c>
+      <c r="R38" s="53">
+        <f t="shared" ref="R38:R41" si="5">H38</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F39" s="18">
+        <v>10</v>
+      </c>
+      <c r="G39" s="18">
+        <v>0</v>
+      </c>
+      <c r="H39" s="18">
+        <v>25</v>
+      </c>
+      <c r="I39" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="52">
+        <v>1</v>
+      </c>
+      <c r="R39" s="53">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G40" s="18">
+        <v>1105</v>
+      </c>
+      <c r="H40" s="18">
+        <v>25</v>
+      </c>
+      <c r="I40" s="18">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="52">
+        <v>1</v>
+      </c>
+      <c r="R40" s="54"/>
+    </row>
+    <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>1731</v>
+      </c>
+      <c r="F41" s="18">
+        <v>7</v>
+      </c>
+      <c r="G41" s="18">
+        <v>0</v>
+      </c>
+      <c r="H41" s="18">
+        <v>30</v>
+      </c>
+      <c r="I41" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>1732</v>
+      </c>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="52">
+        <v>1</v>
+      </c>
+      <c r="R41" s="53">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>1733</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>1734</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>1735</v>
+      </c>
+      <c r="F42" s="18">
+        <v>10</v>
+      </c>
+      <c r="G42" s="18">
+        <v>65</v>
+      </c>
+      <c r="H42" s="18">
+        <v>25</v>
+      </c>
+      <c r="I42" s="18">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="52">
+        <v>1</v>
+      </c>
+      <c r="R42" s="54"/>
+    </row>
+    <row r="43" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F43" s="18">
+        <v>1</v>
+      </c>
+      <c r="G43" s="18">
+        <v>955</v>
+      </c>
+      <c r="H43" s="18">
+        <v>25</v>
+      </c>
+      <c r="I43" s="18">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="52">
+        <v>1</v>
+      </c>
+      <c r="R43" s="54"/>
+    </row>
+    <row r="44" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>1740</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>1741</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G44" s="18">
+        <v>1455</v>
+      </c>
+      <c r="H44" s="18">
+        <v>25</v>
+      </c>
+      <c r="I44" s="18">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="52">
+        <v>1</v>
+      </c>
+      <c r="R44" s="54"/>
+    </row>
+    <row r="45" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>867</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>1742</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="F45" s="18">
+        <v>1</v>
+      </c>
+      <c r="G45" s="18">
+        <v>0</v>
+      </c>
+      <c r="H45" s="18">
+        <v>25</v>
+      </c>
+      <c r="I45" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="52">
+        <v>1</v>
+      </c>
+      <c r="R45" s="53">
+        <f>H45</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F46" s="18">
+        <v>5</v>
+      </c>
+      <c r="G46" s="18">
+        <v>30</v>
+      </c>
+      <c r="H46" s="18">
+        <v>30</v>
+      </c>
+      <c r="I46" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="52">
+        <v>1</v>
+      </c>
+      <c r="R46" s="54"/>
+    </row>
+    <row r="47" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17" t="s">
+        <v>1746</v>
+      </c>
+      <c r="F47" s="18">
+        <v>5</v>
+      </c>
+      <c r="G47" s="18">
+        <v>0</v>
+      </c>
+      <c r="H47" s="18">
+        <v>60</v>
+      </c>
+      <c r="I47" s="18">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="52">
+        <v>1</v>
+      </c>
+      <c r="R47" s="53">
+        <f t="shared" ref="R47:R48" si="6">H47</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17" t="s">
+        <v>1748</v>
+      </c>
+      <c r="F48" s="18">
+        <v>1</v>
+      </c>
+      <c r="G48" s="18">
+        <v>0</v>
+      </c>
+      <c r="H48" s="18">
+        <v>30</v>
+      </c>
+      <c r="I48" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="52">
+        <v>1</v>
+      </c>
+      <c r="R48" s="53">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G50" s="1">
+        <f>SUBTOTAL(9,G3:G49)</f>
+        <v>27010</v>
+      </c>
+      <c r="H50" s="1">
+        <f>SUBTOTAL(9,H3:H49)</f>
+        <v>1390</v>
+      </c>
+      <c r="I50" s="1">
+        <f>SUBTOTAL(9,I3:I49)</f>
+        <v>25620</v>
+      </c>
+      <c r="J50" s="1">
+        <f>SUBTOTAL(9,J3:J49)</f>
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <f>SUBTOTAL(9,K3:K49)</f>
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <f>SUBTOTAL(9,L3:L49)</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <f>SUBTOTAL(9,M3:M49)</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <f>SUBTOTAL(9,N3:N49)</f>
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
+        <f>SUBTOTAL(9,O3:O49)</f>
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <f>SUBTOTAL(9,P3:P49)</f>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <f>SUBTOTAL(9,Q3:Q49)</f>
+        <v>46</v>
+      </c>
+      <c r="R50" s="1">
+        <f>SUBTOTAL(9,R3:R49)</f>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I51" s="26"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I52" s="26"/>
+    </row>
+    <row r="54" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H54" s="4" t="s">
+        <v>1638</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H55" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" s="8">
+        <f>SUM(I49:I53)</f>
+        <v>25620</v>
+      </c>
+      <c r="J55" s="8">
+        <f>Q50</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H56" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="10">
+        <f>R50</f>
+        <v>690</v>
+      </c>
+      <c r="J56" s="11"/>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H57" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="10">
+        <f>S49</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="11"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H58" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="10">
+        <f>T49</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H59" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="10">
+        <f>U49</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="11"/>
+    </row>
+    <row r="60" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H60" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H61" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+    </row>
+    <row r="62" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H62" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="16">
+        <f>SUM(I55:I61)</f>
+        <v>26310</v>
+      </c>
+      <c r="J62" s="16">
+        <f>SUM(J55:J59)</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E64" s="35">
+        <v>7</v>
+      </c>
+      <c r="F64" s="35">
+        <v>960</v>
+      </c>
+      <c r="G64" s="35">
+        <v>0</v>
+      </c>
+      <c r="H64" s="35">
+        <f t="shared" ref="H64:H65" si="7">F64-G64</f>
+        <v>960</v>
+      </c>
+      <c r="I64" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="J64" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K64" s="34" t="s">
+        <v>1643</v>
+      </c>
+      <c r="L64" s="20" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>1715</v>
+      </c>
+      <c r="E65" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="F65" s="35">
+        <v>1965</v>
+      </c>
+      <c r="G65" s="35">
+        <v>0</v>
+      </c>
+      <c r="H65" s="35">
+        <f t="shared" si="7"/>
+        <v>1965</v>
+      </c>
+      <c r="I65" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="J65" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K65" s="34" t="s">
+        <v>1643</v>
+      </c>
+      <c r="L65" s="58" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P48" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P48">
+      <sortCondition ref="J2:J48"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Oct/THÁNG 10.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Oct/THÁNG 10.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Oct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1820BBAE-AC5C-4815-B153-3404A5F0981C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A538F0-0564-4BE4-9C19-5C69FF4ABFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-10" sheetId="4" r:id="rId1"/>
@@ -26,6 +26,8 @@
     <sheet name="13-10" sheetId="14" r:id="rId11"/>
     <sheet name="14-10" sheetId="15" r:id="rId12"/>
     <sheet name="15-10" sheetId="16" r:id="rId13"/>
+    <sheet name="16-10" sheetId="17" r:id="rId14"/>
+    <sheet name="17-10" sheetId="18" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'10-10'!$A$2:$P$32</definedName>
@@ -34,6 +36,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'13-10'!$A$2:$P$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'14-10'!$A$2:$P$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'15-10'!$A$2:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'16-10'!$A$2:$P$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'17-10'!$A$2:$P$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-10'!$A$2:$P$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3-10'!$A$2:$P$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'5-10'!$A$2:$P$84</definedName>
@@ -63,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5087" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5747" uniqueCount="1831">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -4974,6 +4978,588 @@
   </si>
   <si>
     <t>32 ng du. Bến nghé</t>
+  </si>
+  <si>
+    <t>NGAY 16-10</t>
+  </si>
+  <si>
+    <t>Milly Đỗ</t>
+  </si>
+  <si>
+    <t>HD067453</t>
+  </si>
+  <si>
+    <t>14/144/10/7 phạm hùng, bình hưng</t>
+  </si>
+  <si>
+    <t>AT 16-10</t>
+  </si>
+  <si>
+    <t>16-10-2026</t>
+  </si>
+  <si>
+    <t>Bảo Uyên</t>
+  </si>
+  <si>
+    <t>HD067329</t>
+  </si>
+  <si>
+    <t>5606a vinhome grand park ( Đ. cầu vồng, Long Bình)</t>
+  </si>
+  <si>
+    <t>Christy Lương</t>
+  </si>
+  <si>
+    <t>HD067357</t>
+  </si>
+  <si>
+    <t>1079 tạ quang bửu phường bình đông</t>
+  </si>
+  <si>
+    <t>Tran Ngọc</t>
+  </si>
+  <si>
+    <t>HD067400</t>
+  </si>
+  <si>
+    <t>449 lạc long quân phường 5</t>
+  </si>
+  <si>
+    <t>Hồng Nguyễn</t>
+  </si>
+  <si>
+    <t>HD067451</t>
+  </si>
+  <si>
+    <t>621 Tân Kỳ Tân Quý, P. Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Thao Yumi</t>
+  </si>
+  <si>
+    <t>HD067551</t>
+  </si>
+  <si>
+    <t>Số 17, Đường Số 13, Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Đinh Lily</t>
+  </si>
+  <si>
+    <t>HD067487</t>
+  </si>
+  <si>
+    <t>33C Song Hành Quốc Lộ 50, Phong Phú</t>
+  </si>
+  <si>
+    <t>Phạm Vũ Minh Hậu</t>
+  </si>
+  <si>
+    <t>HD067447</t>
+  </si>
+  <si>
+    <t>The Opera Biệt thự Valora Ik6.33 đường số 11, Lk6-33 mới đúng ạ, đường số 11, Xã Bình Hưng</t>
+  </si>
+  <si>
+    <t>Tố Như</t>
+  </si>
+  <si>
+    <t>HD067550</t>
+  </si>
+  <si>
+    <t>688/23/1C Hương Lộ 2, Phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiên Hương</t>
+  </si>
+  <si>
+    <t>HD067544</t>
+  </si>
+  <si>
+    <t>16 đường 168 Phước Long A</t>
+  </si>
+  <si>
+    <t>HD067599</t>
+  </si>
+  <si>
+    <t>38A đường 3158A phạm thế hiển phường bình đông(phuong 7) Đối diệncổng trường THPT nguyễn văn linh</t>
+  </si>
+  <si>
+    <t>KHONGKWAN</t>
+  </si>
+  <si>
+    <t>Ngõ 72 đường 18B, phường Bình Hưng Hòa A</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải ( Bow)</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Chi Nguyen</t>
+  </si>
+  <si>
+    <t>312 Lô G cư xá Thanh Đa, p. Bình Quới</t>
+  </si>
+  <si>
+    <t>.Endny/ HOANG MEO</t>
+  </si>
+  <si>
+    <t>HD067328</t>
+  </si>
+  <si>
+    <t>22, ĐƯỜNG TÂN THỚI NHẤT 1B, PHƯỜNG TÂN THỚI NHẤT</t>
+  </si>
+  <si>
+    <t>Mai Lê</t>
+  </si>
+  <si>
+    <t>HD067391</t>
+  </si>
+  <si>
+    <t>204/B12 Nguyễn văn hưởng, p thảo điền</t>
+  </si>
+  <si>
+    <t>HD067368</t>
+  </si>
+  <si>
+    <t>Thanh Thảo Sumi</t>
+  </si>
+  <si>
+    <t>HD067392</t>
+  </si>
+  <si>
+    <t>Căn 16.07 toà A2 chung cư Hoàng Anh River View, số 37 đường Nguyễn Văn Hưởng, phường An Khánh (phường cũ là Thảo Điền)</t>
+  </si>
+  <si>
+    <t>HD067598</t>
+  </si>
+  <si>
+    <t>Trần Thảo Anh</t>
+  </si>
+  <si>
+    <t>HD067567</t>
+  </si>
+  <si>
+    <t>Veronica Nhà Màu Vàng, 216/26, Nguyễn Văn Hưởng, Phường An Khánh</t>
+  </si>
+  <si>
+    <t>HD067573</t>
+  </si>
+  <si>
+    <t>Hằng Kimm</t>
+  </si>
+  <si>
+    <t>HD067330</t>
+  </si>
+  <si>
+    <t>31/3 ung văn khiêm thạnh mỹ tây</t>
+  </si>
+  <si>
+    <t>Chế Vân</t>
+  </si>
+  <si>
+    <t>HD067563</t>
+  </si>
+  <si>
+    <t>496/1/56 dương quảng hàm phường an nhơn</t>
+  </si>
+  <si>
+    <t>Vũ Thị Hà</t>
+  </si>
+  <si>
+    <t>HD067607</t>
+  </si>
+  <si>
+    <t>20 vũ tông phan</t>
+  </si>
+  <si>
+    <t>Bảo Như</t>
+  </si>
+  <si>
+    <t>HD067374</t>
+  </si>
+  <si>
+    <t>e208 nguyễn hữu cảnh p22 toà nhà landmark 3</t>
+  </si>
+  <si>
+    <t>andu dang</t>
+  </si>
+  <si>
+    <t>24/5G, Ấp Đông Lân, Xã Bà Điểm</t>
+  </si>
+  <si>
+    <t>Trân Helen</t>
+  </si>
+  <si>
+    <t>HD067483</t>
+  </si>
+  <si>
+    <t>36/15 Yên Thế, Phường Tân Sơn Hoà, Phường Tân Bình</t>
+  </si>
+  <si>
+    <t>HD067386</t>
+  </si>
+  <si>
+    <t>Saigon riverside complex (block C1) Số 4 đào trí phú thuận</t>
+  </si>
+  <si>
+    <t>Thanh Hiền</t>
+  </si>
+  <si>
+    <t>HD067569</t>
+  </si>
+  <si>
+    <t>Block D1, Chung cư Hoàng Anh Gia Lai 3, Đường Nguyễn Hữu Thọ, xã Phước Kiển</t>
+  </si>
+  <si>
+    <t>kh ck shop 1965k</t>
+  </si>
+  <si>
+    <t>Việt Trinh</t>
+  </si>
+  <si>
+    <t>HD067371</t>
+  </si>
+  <si>
+    <t>Số 42, Đường Phùng Hưng Phường Chợ Lớn</t>
+  </si>
+  <si>
+    <t>HD067377</t>
+  </si>
+  <si>
+    <t>chung cư sunrise city view block B</t>
+  </si>
+  <si>
+    <t>HD067527</t>
+  </si>
+  <si>
+    <t>156 Trần Nhân Tôn, phường Vườn Lài (phường 2)</t>
+  </si>
+  <si>
+    <t>Veriska Erica</t>
+  </si>
+  <si>
+    <t>HD067552</t>
+  </si>
+  <si>
+    <t>Lan Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD067596</t>
+  </si>
+  <si>
+    <t>96 hoàng hoa thám</t>
+  </si>
+  <si>
+    <t>THI (KT Ng)</t>
+  </si>
+  <si>
+    <t>HD067570</t>
+  </si>
+  <si>
+    <t>39 Nguyen thi Thap khu dan cu him lam phuong tan hung ( me in nail)</t>
+  </si>
+  <si>
+    <t>kh ck shop 960k</t>
+  </si>
+  <si>
+    <t>Dinh Luong</t>
+  </si>
+  <si>
+    <t>HD067500</t>
+  </si>
+  <si>
+    <t>246 nguyễn duy dương f4</t>
+  </si>
+  <si>
+    <t>Ngọc Hiền</t>
+  </si>
+  <si>
+    <t>HD067584</t>
+  </si>
+  <si>
+    <t>13c lê thánh tôn</t>
+  </si>
+  <si>
+    <t>Jessicaa</t>
+  </si>
+  <si>
+    <t>HD067352</t>
+  </si>
+  <si>
+    <t>17A Cộng Hòa, Tân Sơn Nhất</t>
+  </si>
+  <si>
+    <t>HD067601</t>
+  </si>
+  <si>
+    <t>phương uyên</t>
+  </si>
+  <si>
+    <t>290 An Dương Vương phường 4 (phường Chợ Quán mới)</t>
+  </si>
+  <si>
+    <t>Minea</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương, Phường 9</t>
+  </si>
+  <si>
+    <t>DaRaVin</t>
+  </si>
+  <si>
+    <t>301 Phạm Ngũ Lão, Phường Phạm Ngũ Lão</t>
+  </si>
+  <si>
+    <t>T6.16.10.2026</t>
+  </si>
+  <si>
+    <t>NGAY 17-10</t>
+  </si>
+  <si>
+    <t>T7.17.10.2026</t>
+  </si>
+  <si>
+    <t>Thảo Đoàn</t>
+  </si>
+  <si>
+    <t>HD067832</t>
+  </si>
+  <si>
+    <t>1041 Hồng Bàng, P.Phú Lâm</t>
+  </si>
+  <si>
+    <t>AT 17-10</t>
+  </si>
+  <si>
+    <t>17-10-2026</t>
+  </si>
+  <si>
+    <t>Lê Huyền Trang</t>
+  </si>
+  <si>
+    <t>HD067663</t>
+  </si>
+  <si>
+    <t>61 Đặng Minh Trứ phường Bảy Hiền</t>
+  </si>
+  <si>
+    <t>HD067687</t>
+  </si>
+  <si>
+    <t>Ngọc GiÀu</t>
+  </si>
+  <si>
+    <t>HD067791</t>
+  </si>
+  <si>
+    <t>207 trần văn kiểu phường bình phú</t>
+  </si>
+  <si>
+    <t>Lữ Nhung Lữ Nhung</t>
+  </si>
+  <si>
+    <t>HD067826</t>
+  </si>
+  <si>
+    <t>28 Tân hương phường Phú Thọ Hòa</t>
+  </si>
+  <si>
+    <t>Tuyết Nhi</t>
+  </si>
+  <si>
+    <t>417 Hậu Giang</t>
+  </si>
+  <si>
+    <t>HD067789</t>
+  </si>
+  <si>
+    <t>107 đường 4 khu tái định cư 680ha khu phố 11 linh xuân</t>
+  </si>
+  <si>
+    <t>HD067779</t>
+  </si>
+  <si>
+    <t>Nguyen Hoang Ngoc Anh</t>
+  </si>
+  <si>
+    <t>HD067637</t>
+  </si>
+  <si>
+    <t>44/36 đông hưng thuận 6 phường tân hưng thuận</t>
+  </si>
+  <si>
+    <t>W2488</t>
+  </si>
+  <si>
+    <t>HD067898</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, Thới An</t>
+  </si>
+  <si>
+    <t>(Anna Hanh )</t>
+  </si>
+  <si>
+    <t>HD067782</t>
+  </si>
+  <si>
+    <t>188 Nguyễn Văn Công, P.3</t>
+  </si>
+  <si>
+    <t>HD067735</t>
+  </si>
+  <si>
+    <t>Nhi Phan</t>
+  </si>
+  <si>
+    <t>HD067698</t>
+  </si>
+  <si>
+    <t>22 TÂN THỚI NHẤT 1B, Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Vy</t>
+  </si>
+  <si>
+    <t>HD067665</t>
+  </si>
+  <si>
+    <t>Số 6 hẻm 153 đường quốc lộ 13, phường 26</t>
+  </si>
+  <si>
+    <t>W2429</t>
+  </si>
+  <si>
+    <t>HD067615</t>
+  </si>
+  <si>
+    <t>WIND XPRESS ( vận chuyển Việt -&gt; thái ) Số 68 . Tân thới hiệp 14</t>
+  </si>
+  <si>
+    <t>Candy Kim</t>
+  </si>
+  <si>
+    <t>HD067682</t>
+  </si>
+  <si>
+    <t>31/23 đường làng tăng phú phường tăng nhơn phú a</t>
+  </si>
+  <si>
+    <t>Soya Su</t>
+  </si>
+  <si>
+    <t>HD067696</t>
+  </si>
+  <si>
+    <t>102 man thiện</t>
+  </si>
+  <si>
+    <t>Hiếu Phan</t>
+  </si>
+  <si>
+    <t>HD067816</t>
+  </si>
+  <si>
+    <t>BS10A vinhomes grand park phường long bình</t>
+  </si>
+  <si>
+    <t>Bé Lan</t>
+  </si>
+  <si>
+    <t>HD067852</t>
+  </si>
+  <si>
+    <t>95 đường 59, P14</t>
+  </si>
+  <si>
+    <t>( Cẩm Giang) Kim Sarang</t>
+  </si>
+  <si>
+    <t>HD067864</t>
+  </si>
+  <si>
+    <t>Phong 1407 –Block B - Chung cư Opal Riverside, Đường Số 2, Phường Hiệp Bình</t>
+  </si>
+  <si>
+    <t>Thúy</t>
+  </si>
+  <si>
+    <t>HD067851</t>
+  </si>
+  <si>
+    <t>103/14B Trần Quang Diệu P Nhiêu Lộc</t>
+  </si>
+  <si>
+    <t>Vương Huệ</t>
+  </si>
+  <si>
+    <t>HD067681</t>
+  </si>
+  <si>
+    <t>80 đg số 3 tân kiếng</t>
+  </si>
+  <si>
+    <t>huyền nguyễn</t>
+  </si>
+  <si>
+    <t>HD067857</t>
+  </si>
+  <si>
+    <t>243/44/12 tôn đản p15</t>
+  </si>
+  <si>
+    <t>Như Lê</t>
+  </si>
+  <si>
+    <t>HD067675</t>
+  </si>
+  <si>
+    <t>95/70/2 lê văn lương phường tân hưng</t>
+  </si>
+  <si>
+    <t>Jessie Beauty</t>
+  </si>
+  <si>
+    <t>HD067697</t>
+  </si>
+  <si>
+    <t>Đặng Trinh ( phòng 103 )</t>
+  </si>
+  <si>
+    <t>HD067755</t>
+  </si>
+  <si>
+    <t>406/35 Cộng Hòa, Phường 13</t>
+  </si>
+  <si>
+    <t>Linh Trần</t>
+  </si>
+  <si>
+    <t>HD067700</t>
+  </si>
+  <si>
+    <t>132 Bến Vân Đồn phường 6</t>
+  </si>
+  <si>
+    <t>Thư</t>
+  </si>
+  <si>
+    <t>HD067829</t>
+  </si>
+  <si>
+    <t>76 trần đình xu</t>
+  </si>
+  <si>
+    <t>Fangfang</t>
+  </si>
+  <si>
+    <t>A75/6B/2 Bạch Đằng,Phường 2</t>
+  </si>
+  <si>
+    <t>đơn trả 19.10</t>
   </si>
 </sst>
 </file>
@@ -5143,7 +5729,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -5166,13 +5752,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5247,6 +5855,13 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18507,51 +19122,51 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G45" s="1">
-        <f>SUBTOTAL(9,G3:G44)</f>
+        <f t="shared" ref="G45:R45" si="4">SUBTOTAL(9,G3:G44)</f>
         <v>35265</v>
       </c>
       <c r="H45" s="1">
-        <f>SUBTOTAL(9,H3:H44)</f>
+        <f t="shared" si="4"/>
         <v>1220</v>
       </c>
       <c r="I45" s="1">
-        <f>SUBTOTAL(9,I3:I44)</f>
+        <f t="shared" si="4"/>
         <v>34045</v>
       </c>
       <c r="J45" s="1">
-        <f>SUBTOTAL(9,J3:J44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K45" s="1">
-        <f>SUBTOTAL(9,K3:K44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L45" s="1">
-        <f>SUBTOTAL(9,L3:L44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M45" s="1">
-        <f>SUBTOTAL(9,M3:M44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N45" s="1">
-        <f>SUBTOTAL(9,N3:N44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O45" s="1">
-        <f>SUBTOTAL(9,O3:O44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P45" s="1">
-        <f>SUBTOTAL(9,P3:P44)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q45" s="1">
-        <f>SUBTOTAL(9,Q3:Q44)</f>
+        <f t="shared" si="4"/>
         <v>41</v>
       </c>
       <c r="R45" s="1">
-        <f>SUBTOTAL(9,R3:R44)</f>
+        <f t="shared" si="4"/>
         <v>415</v>
       </c>
     </row>
@@ -18703,6 +19318,4105 @@
   <autoFilter ref="A2:P43" xr:uid="{00000000-0009-0000-0000-000006000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P43">
       <sortCondition ref="J2:J43"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E58806-57C6-4430-9673-0F164803219C}">
+  <dimension ref="A1:R65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>1638</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>1639</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>1640</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="18">
+        <v>3850</v>
+      </c>
+      <c r="H3" s="18">
+        <v>45</v>
+      </c>
+      <c r="I3" s="18">
+        <f t="shared" ref="I3:I48" si="0">G3-H3</f>
+        <v>3805</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="52">
+        <v>1</v>
+      </c>
+      <c r="R3" s="53">
+        <f>H3</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F4" s="18">
+        <v>9</v>
+      </c>
+      <c r="G4" s="18">
+        <v>820</v>
+      </c>
+      <c r="H4" s="18">
+        <v>30</v>
+      </c>
+      <c r="I4" s="18">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="52">
+        <v>1</v>
+      </c>
+      <c r="R4" s="54"/>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F5" s="18">
+        <v>8</v>
+      </c>
+      <c r="G5" s="18">
+        <v>950</v>
+      </c>
+      <c r="H5" s="18">
+        <v>30</v>
+      </c>
+      <c r="I5" s="18">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="52">
+        <v>1</v>
+      </c>
+      <c r="R5" s="54"/>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>1651</v>
+      </c>
+      <c r="F6" s="18">
+        <v>11</v>
+      </c>
+      <c r="G6" s="18">
+        <v>1575</v>
+      </c>
+      <c r="H6" s="18">
+        <v>25</v>
+      </c>
+      <c r="I6" s="18">
+        <f t="shared" si="0"/>
+        <v>1550</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="52">
+        <v>1</v>
+      </c>
+      <c r="R6" s="54"/>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>1654</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="18">
+        <v>790</v>
+      </c>
+      <c r="H7" s="18">
+        <v>30</v>
+      </c>
+      <c r="I7" s="18">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="52">
+        <v>1</v>
+      </c>
+      <c r="R7" s="54"/>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="18">
+        <v>1110</v>
+      </c>
+      <c r="H8" s="18">
+        <v>30</v>
+      </c>
+      <c r="I8" s="18">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="52">
+        <v>1</v>
+      </c>
+      <c r="R8" s="54"/>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>1659</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>1660</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="18">
+        <v>905</v>
+      </c>
+      <c r="H9" s="18">
+        <v>35</v>
+      </c>
+      <c r="I9" s="18">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="52">
+        <v>1</v>
+      </c>
+      <c r="R9" s="54"/>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <v>35</v>
+      </c>
+      <c r="I10" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="52">
+        <v>1</v>
+      </c>
+      <c r="R10" s="53">
+        <f t="shared" ref="R10:R11" si="1">H10</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18">
+        <v>30</v>
+      </c>
+      <c r="I11" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="52">
+        <v>1</v>
+      </c>
+      <c r="R11" s="53">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F12" s="18">
+        <v>9</v>
+      </c>
+      <c r="G12" s="18">
+        <v>460</v>
+      </c>
+      <c r="H12" s="18">
+        <v>30</v>
+      </c>
+      <c r="I12" s="18">
+        <f t="shared" si="0"/>
+        <v>430</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="52">
+        <v>1</v>
+      </c>
+      <c r="R12" s="54"/>
+    </row>
+    <row r="13" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>1671</v>
+      </c>
+      <c r="F13" s="22">
+        <v>8</v>
+      </c>
+      <c r="G13" s="22">
+        <v>170</v>
+      </c>
+      <c r="H13" s="22">
+        <v>30</v>
+      </c>
+      <c r="I13" s="22">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="55">
+        <v>1</v>
+      </c>
+      <c r="R13" s="56"/>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="18">
+        <v>2140</v>
+      </c>
+      <c r="H14" s="18">
+        <v>40</v>
+      </c>
+      <c r="I14" s="18">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="52">
+        <v>1</v>
+      </c>
+      <c r="R14" s="54"/>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <v>35</v>
+      </c>
+      <c r="I15" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="52">
+        <v>1</v>
+      </c>
+      <c r="R15" s="53">
+        <f t="shared" ref="R15:R19" si="2">H15</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17" t="s">
+        <v>1673</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <v>35</v>
+      </c>
+      <c r="I16" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="52">
+        <v>1</v>
+      </c>
+      <c r="R16" s="53">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="18">
+        <v>0</v>
+      </c>
+      <c r="H17" s="18">
+        <v>35</v>
+      </c>
+      <c r="I17" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>1641</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="52">
+        <v>1</v>
+      </c>
+      <c r="R17" s="53">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="22">
+        <v>0</v>
+      </c>
+      <c r="H18" s="22">
+        <v>20</v>
+      </c>
+      <c r="I18" s="22">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N18" s="21"/>
+      <c r="O18" s="21"/>
+      <c r="P18" s="21"/>
+      <c r="Q18" s="55">
+        <v>1</v>
+      </c>
+      <c r="R18" s="57">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>1678</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>1679</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F19" s="18">
+        <v>12</v>
+      </c>
+      <c r="G19" s="18">
+        <v>0</v>
+      </c>
+      <c r="H19" s="18">
+        <v>30</v>
+      </c>
+      <c r="I19" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="52">
+        <v>1</v>
+      </c>
+      <c r="R19" s="53">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>1682</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F20" s="18">
+        <v>2</v>
+      </c>
+      <c r="G20" s="18">
+        <v>1070</v>
+      </c>
+      <c r="H20" s="18">
+        <v>30</v>
+      </c>
+      <c r="I20" s="18">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="52">
+        <v>1</v>
+      </c>
+      <c r="R20" s="54"/>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="18">
+        <v>0</v>
+      </c>
+      <c r="H21" s="18">
+        <v>30</v>
+      </c>
+      <c r="I21" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="52">
+        <v>1</v>
+      </c>
+      <c r="R21" s="53">
+        <f>H21</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>1685</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F22" s="18">
+        <v>2</v>
+      </c>
+      <c r="G22" s="18">
+        <v>720</v>
+      </c>
+      <c r="H22" s="18">
+        <v>30</v>
+      </c>
+      <c r="I22" s="18">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="52">
+        <v>1</v>
+      </c>
+      <c r="R22" s="54"/>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="18">
+        <v>1210</v>
+      </c>
+      <c r="H23" s="18">
+        <v>20</v>
+      </c>
+      <c r="I23" s="18">
+        <f t="shared" si="0"/>
+        <v>1190</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="52">
+        <v>1</v>
+      </c>
+      <c r="R23" s="54"/>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F24" s="18">
+        <v>2</v>
+      </c>
+      <c r="G24" s="18">
+        <v>920</v>
+      </c>
+      <c r="H24" s="18">
+        <v>30</v>
+      </c>
+      <c r="I24" s="18">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="52">
+        <v>1</v>
+      </c>
+      <c r="R24" s="54"/>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F25" s="18">
+        <v>2</v>
+      </c>
+      <c r="G25" s="18">
+        <v>960</v>
+      </c>
+      <c r="H25" s="18">
+        <v>0</v>
+      </c>
+      <c r="I25" s="18">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="52">
+        <v>1</v>
+      </c>
+      <c r="R25" s="54"/>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="18">
+        <v>510</v>
+      </c>
+      <c r="H26" s="18">
+        <v>20</v>
+      </c>
+      <c r="I26" s="18">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="52">
+        <v>1</v>
+      </c>
+      <c r="R26" s="54"/>
+    </row>
+    <row r="27" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>1697</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>1698</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="22">
+        <v>25</v>
+      </c>
+      <c r="H27" s="22">
+        <v>25</v>
+      </c>
+      <c r="I27" s="22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="55">
+        <v>1</v>
+      </c>
+      <c r="R27" s="56"/>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>1701</v>
+      </c>
+      <c r="F28" s="18">
+        <v>2</v>
+      </c>
+      <c r="G28" s="18">
+        <v>1090</v>
+      </c>
+      <c r="H28" s="18">
+        <v>30</v>
+      </c>
+      <c r="I28" s="18">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="52">
+        <v>1</v>
+      </c>
+      <c r="R28" s="54"/>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>1702</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>1703</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>1704</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="18">
+        <v>950</v>
+      </c>
+      <c r="H29" s="18">
+        <v>20</v>
+      </c>
+      <c r="I29" s="18">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="52">
+        <v>1</v>
+      </c>
+      <c r="R29" s="54"/>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17" t="s">
+        <v>1706</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" s="18">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18">
+        <v>70</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="0"/>
+        <v>-70</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="52">
+        <v>1</v>
+      </c>
+      <c r="R30" s="53">
+        <f t="shared" ref="R30:R33" si="3">H30</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="18">
+        <v>12</v>
+      </c>
+      <c r="G31" s="18">
+        <v>0</v>
+      </c>
+      <c r="H31" s="18">
+        <v>35</v>
+      </c>
+      <c r="I31" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="52">
+        <v>1</v>
+      </c>
+      <c r="R31" s="53">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>992</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="F32" s="18">
+        <v>12</v>
+      </c>
+      <c r="G32" s="18">
+        <v>0</v>
+      </c>
+      <c r="H32" s="18">
+        <v>35</v>
+      </c>
+      <c r="I32" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="52">
+        <v>1</v>
+      </c>
+      <c r="R32" s="53">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>1708</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>1709</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G33" s="18">
+        <v>0</v>
+      </c>
+      <c r="H33" s="18">
+        <v>25</v>
+      </c>
+      <c r="I33" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="52">
+        <v>1</v>
+      </c>
+      <c r="R33" s="53">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>807</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="F34" s="18">
+        <v>7</v>
+      </c>
+      <c r="G34" s="18">
+        <v>1510</v>
+      </c>
+      <c r="H34" s="18">
+        <v>30</v>
+      </c>
+      <c r="I34" s="18">
+        <f t="shared" si="0"/>
+        <v>1480</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M34" s="17"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="52">
+        <v>1</v>
+      </c>
+      <c r="R34" s="54"/>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>1714</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="G35" s="18">
+        <v>0</v>
+      </c>
+      <c r="H35" s="18">
+        <v>35</v>
+      </c>
+      <c r="I35" s="18">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M35" s="49" t="s">
+        <v>1715</v>
+      </c>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="52">
+        <v>1</v>
+      </c>
+      <c r="R35" s="53">
+        <f t="shared" ref="R35" si="4">H35</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F36" s="18">
+        <v>5</v>
+      </c>
+      <c r="G36" s="18">
+        <v>785</v>
+      </c>
+      <c r="H36" s="18">
+        <v>25</v>
+      </c>
+      <c r="I36" s="18">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M36" s="17"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="52">
+        <v>1</v>
+      </c>
+      <c r="R36" s="54"/>
+    </row>
+    <row r="37" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>1719</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>1720</v>
+      </c>
+      <c r="F37" s="18">
+        <v>7</v>
+      </c>
+      <c r="G37" s="18">
+        <v>880</v>
+      </c>
+      <c r="H37" s="18">
+        <v>30</v>
+      </c>
+      <c r="I37" s="18">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="52">
+        <v>1</v>
+      </c>
+      <c r="R37" s="54"/>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="17"/>
+      <c r="B38" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>1722</v>
+      </c>
+      <c r="F38" s="18">
+        <v>10</v>
+      </c>
+      <c r="G38" s="18">
+        <v>0</v>
+      </c>
+      <c r="H38" s="18">
+        <v>25</v>
+      </c>
+      <c r="I38" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M38" s="17"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="52">
+        <v>1</v>
+      </c>
+      <c r="R38" s="53">
+        <f t="shared" ref="R38:R41" si="5">H38</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="17"/>
+      <c r="B39" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>1723</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F39" s="18">
+        <v>10</v>
+      </c>
+      <c r="G39" s="18">
+        <v>0</v>
+      </c>
+      <c r="H39" s="18">
+        <v>25</v>
+      </c>
+      <c r="I39" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="52">
+        <v>1</v>
+      </c>
+      <c r="R39" s="53">
+        <f t="shared" si="5"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>1726</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G40" s="18">
+        <v>1105</v>
+      </c>
+      <c r="H40" s="18">
+        <v>25</v>
+      </c>
+      <c r="I40" s="18">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="52">
+        <v>1</v>
+      </c>
+      <c r="R40" s="54"/>
+    </row>
+    <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>1728</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>1729</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>1730</v>
+      </c>
+      <c r="F41" s="18">
+        <v>7</v>
+      </c>
+      <c r="G41" s="18">
+        <v>0</v>
+      </c>
+      <c r="H41" s="18">
+        <v>30</v>
+      </c>
+      <c r="I41" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>1731</v>
+      </c>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="52">
+        <v>1</v>
+      </c>
+      <c r="R41" s="53">
+        <f t="shared" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>1733</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F42" s="18">
+        <v>10</v>
+      </c>
+      <c r="G42" s="18">
+        <v>65</v>
+      </c>
+      <c r="H42" s="18">
+        <v>25</v>
+      </c>
+      <c r="I42" s="18">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M42" s="17"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="52">
+        <v>1</v>
+      </c>
+      <c r="R42" s="54"/>
+    </row>
+    <row r="43" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F43" s="18">
+        <v>1</v>
+      </c>
+      <c r="G43" s="18">
+        <v>955</v>
+      </c>
+      <c r="H43" s="18">
+        <v>25</v>
+      </c>
+      <c r="I43" s="18">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="52">
+        <v>1</v>
+      </c>
+      <c r="R43" s="54"/>
+    </row>
+    <row r="44" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>1739</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G44" s="18">
+        <v>1455</v>
+      </c>
+      <c r="H44" s="18">
+        <v>25</v>
+      </c>
+      <c r="I44" s="18">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="52">
+        <v>1</v>
+      </c>
+      <c r="R44" s="54"/>
+    </row>
+    <row r="45" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>867</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="F45" s="18">
+        <v>1</v>
+      </c>
+      <c r="G45" s="18">
+        <v>0</v>
+      </c>
+      <c r="H45" s="18">
+        <v>25</v>
+      </c>
+      <c r="I45" s="18">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="52">
+        <v>1</v>
+      </c>
+      <c r="R45" s="53">
+        <f>H45</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17" t="s">
+        <v>1743</v>
+      </c>
+      <c r="F46" s="18">
+        <v>5</v>
+      </c>
+      <c r="G46" s="18">
+        <v>30</v>
+      </c>
+      <c r="H46" s="18">
+        <v>30</v>
+      </c>
+      <c r="I46" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="52">
+        <v>1</v>
+      </c>
+      <c r="R46" s="54"/>
+    </row>
+    <row r="47" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F47" s="18">
+        <v>5</v>
+      </c>
+      <c r="G47" s="18">
+        <v>0</v>
+      </c>
+      <c r="H47" s="18">
+        <v>60</v>
+      </c>
+      <c r="I47" s="18">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="52">
+        <v>1</v>
+      </c>
+      <c r="R47" s="53">
+        <f t="shared" ref="R47:R48" si="6">H47</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17" t="s">
+        <v>1747</v>
+      </c>
+      <c r="F48" s="18">
+        <v>1</v>
+      </c>
+      <c r="G48" s="18">
+        <v>0</v>
+      </c>
+      <c r="H48" s="18">
+        <v>30</v>
+      </c>
+      <c r="I48" s="18">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" s="17" t="s">
+        <v>1642</v>
+      </c>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="52">
+        <v>1</v>
+      </c>
+      <c r="R48" s="53">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G50" s="1">
+        <f t="shared" ref="G50:R50" si="7">SUBTOTAL(9,G3:G49)</f>
+        <v>27010</v>
+      </c>
+      <c r="H50" s="1">
+        <f t="shared" si="7"/>
+        <v>1390</v>
+      </c>
+      <c r="I50" s="1">
+        <f t="shared" si="7"/>
+        <v>25620</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="R50" s="1">
+        <f t="shared" si="7"/>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I51" s="26"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I52" s="26"/>
+    </row>
+    <row r="54" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H54" s="4" t="s">
+        <v>1748</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H55" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" s="8">
+        <f>SUM(I49:I53)</f>
+        <v>25620</v>
+      </c>
+      <c r="J55" s="8">
+        <f>Q50</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H56" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="10">
+        <f>R50</f>
+        <v>690</v>
+      </c>
+      <c r="J56" s="11"/>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H57" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="10">
+        <f>S49</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="11"/>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H58" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="10">
+        <f>T49</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H59" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="10">
+        <f>U49</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="11"/>
+    </row>
+    <row r="60" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H60" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+    </row>
+    <row r="61" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H61" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+    </row>
+    <row r="62" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H62" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="16">
+        <f>SUM(I55:I61)</f>
+        <v>26310</v>
+      </c>
+      <c r="J62" s="16">
+        <f>SUM(J55:J59)</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>1730</v>
+      </c>
+      <c r="E64" s="35">
+        <v>7</v>
+      </c>
+      <c r="F64" s="35">
+        <v>960</v>
+      </c>
+      <c r="G64" s="35">
+        <v>0</v>
+      </c>
+      <c r="H64" s="35">
+        <f t="shared" ref="H64:H65" si="8">F64-G64</f>
+        <v>960</v>
+      </c>
+      <c r="I64" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="J64" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K64" s="34" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L64" s="20" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E65" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="F65" s="35">
+        <v>1965</v>
+      </c>
+      <c r="G65" s="35">
+        <v>0</v>
+      </c>
+      <c r="H65" s="35">
+        <f t="shared" si="8"/>
+        <v>1965</v>
+      </c>
+      <c r="I65" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="J65" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="K65" s="34" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L65" s="58" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P48" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P48">
+      <sortCondition ref="J2:J48"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91829BF7-D518-40F6-A701-0CE8C521B288}">
+  <dimension ref="A1:R49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F3" s="18">
+        <v>6</v>
+      </c>
+      <c r="G3" s="18">
+        <v>955</v>
+      </c>
+      <c r="H3" s="18">
+        <v>25</v>
+      </c>
+      <c r="I3" s="18">
+        <f>G3-H3</f>
+        <v>930</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>1757</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>1758</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="18">
+        <v>945</v>
+      </c>
+      <c r="H4" s="18">
+        <v>25</v>
+      </c>
+      <c r="I4" s="18">
+        <f>G4-H4</f>
+        <v>920</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18">
+        <v>1750</v>
+      </c>
+      <c r="H5" s="18">
+        <v>30</v>
+      </c>
+      <c r="I5" s="18">
+        <f>G5-H5</f>
+        <v>1720</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>1760</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>1761</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>1762</v>
+      </c>
+      <c r="F6" s="18">
+        <v>6</v>
+      </c>
+      <c r="G6" s="18">
+        <v>855</v>
+      </c>
+      <c r="H6" s="18">
+        <v>25</v>
+      </c>
+      <c r="I6" s="18">
+        <f>G6-H6</f>
+        <v>830</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G7" s="18">
+        <v>645</v>
+      </c>
+      <c r="H7" s="18">
+        <v>25</v>
+      </c>
+      <c r="I7" s="18">
+        <f>G7-H7</f>
+        <v>620</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17" t="s">
+        <v>1767</v>
+      </c>
+      <c r="F8" s="18">
+        <v>6</v>
+      </c>
+      <c r="G8" s="18">
+        <v>600</v>
+      </c>
+      <c r="H8" s="18">
+        <v>30</v>
+      </c>
+      <c r="I8" s="18">
+        <f>G8-H8</f>
+        <v>570</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="18">
+        <v>13880</v>
+      </c>
+      <c r="H9" s="18">
+        <v>80</v>
+      </c>
+      <c r="I9" s="18">
+        <f>G9-H9</f>
+        <v>13800</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>1754</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="47" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="18">
+        <v>860</v>
+      </c>
+      <c r="H10" s="18">
+        <v>30</v>
+      </c>
+      <c r="I10" s="18">
+        <f>G10-H10</f>
+        <v>830</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="18">
+        <v>955</v>
+      </c>
+      <c r="H11" s="18">
+        <v>25</v>
+      </c>
+      <c r="I11" s="18">
+        <f>G11-H11</f>
+        <v>930</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>1773</v>
+      </c>
+      <c r="F12" s="18">
+        <v>12</v>
+      </c>
+      <c r="G12" s="18">
+        <v>790</v>
+      </c>
+      <c r="H12" s="18">
+        <v>30</v>
+      </c>
+      <c r="I12" s="18">
+        <f>G12-H12</f>
+        <v>760</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F13" s="18">
+        <v>12</v>
+      </c>
+      <c r="G13" s="18">
+        <v>0</v>
+      </c>
+      <c r="H13" s="18">
+        <v>30</v>
+      </c>
+      <c r="I13" s="18">
+        <f>G13-H13</f>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17">
+        <v>1</v>
+      </c>
+      <c r="R13" s="19">
+        <f>H13</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="18">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
+        <v>25</v>
+      </c>
+      <c r="I14" s="18">
+        <f>G14-H14</f>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17">
+        <v>1</v>
+      </c>
+      <c r="R14" s="19">
+        <f>H14</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F15" s="18">
+        <v>9</v>
+      </c>
+      <c r="G15" s="18">
+        <v>1110</v>
+      </c>
+      <c r="H15" s="18">
+        <v>30</v>
+      </c>
+      <c r="I15" s="18">
+        <f>G15-H15</f>
+        <v>1080</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F16" s="18">
+        <v>12</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <v>30</v>
+      </c>
+      <c r="I16" s="18">
+        <f>G16-H16</f>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17">
+        <v>1</v>
+      </c>
+      <c r="R16" s="19">
+        <f t="shared" ref="R16:R18" si="0">H16</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="18">
+        <v>0</v>
+      </c>
+      <c r="H17" s="18">
+        <v>20</v>
+      </c>
+      <c r="I17" s="18">
+        <f>G17-H17</f>
+        <v>-20</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17">
+        <v>1</v>
+      </c>
+      <c r="R17" s="19">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>1788</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>1789</v>
+      </c>
+      <c r="F18" s="18">
+        <v>12</v>
+      </c>
+      <c r="G18" s="18">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18">
+        <v>30</v>
+      </c>
+      <c r="I18" s="18">
+        <f>G18-H18</f>
+        <v>-30</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17">
+        <v>1</v>
+      </c>
+      <c r="R18" s="19">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F19" s="18">
+        <v>9</v>
+      </c>
+      <c r="G19" s="18">
+        <v>820</v>
+      </c>
+      <c r="H19" s="18">
+        <v>30</v>
+      </c>
+      <c r="I19" s="18">
+        <f>G19-H19</f>
+        <v>790</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>1794</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>1795</v>
+      </c>
+      <c r="F20" s="18">
+        <v>9</v>
+      </c>
+      <c r="G20" s="18">
+        <v>900</v>
+      </c>
+      <c r="H20" s="18">
+        <v>30</v>
+      </c>
+      <c r="I20" s="18">
+        <f>G20-H20</f>
+        <v>870</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>1798</v>
+      </c>
+      <c r="F21" s="18">
+        <v>9</v>
+      </c>
+      <c r="G21" s="18">
+        <v>1110</v>
+      </c>
+      <c r="H21" s="18">
+        <v>30</v>
+      </c>
+      <c r="I21" s="18">
+        <f>G21-H21</f>
+        <v>1080</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="18">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18">
+        <v>25</v>
+      </c>
+      <c r="I22" s="18">
+        <f>G22-H22</f>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17">
+        <v>1</v>
+      </c>
+      <c r="R22" s="19">
+        <f>H22</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="18">
+        <v>1090</v>
+      </c>
+      <c r="H23" s="18">
+        <v>30</v>
+      </c>
+      <c r="I23" s="18">
+        <f>G23-H23</f>
+        <v>1060</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>1806</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>1807</v>
+      </c>
+      <c r="F24" s="18">
+        <v>3</v>
+      </c>
+      <c r="G24" s="18">
+        <v>855</v>
+      </c>
+      <c r="H24" s="18">
+        <v>25</v>
+      </c>
+      <c r="I24" s="18">
+        <f>G24-H24</f>
+        <v>830</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>1809</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>1810</v>
+      </c>
+      <c r="F25" s="18">
+        <v>7</v>
+      </c>
+      <c r="G25" s="18">
+        <v>920</v>
+      </c>
+      <c r="H25" s="18">
+        <v>30</v>
+      </c>
+      <c r="I25" s="18">
+        <f>G25-H25</f>
+        <v>890</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F26" s="18">
+        <v>4</v>
+      </c>
+      <c r="G26" s="18">
+        <v>1035</v>
+      </c>
+      <c r="H26" s="18">
+        <v>25</v>
+      </c>
+      <c r="I26" s="18">
+        <f>G26-H26</f>
+        <v>1010</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F27" s="18">
+        <v>7</v>
+      </c>
+      <c r="G27" s="18">
+        <v>960</v>
+      </c>
+      <c r="H27" s="18">
+        <v>30</v>
+      </c>
+      <c r="I27" s="18">
+        <f>G27-H27</f>
+        <v>930</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M27" s="17"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>597</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="18">
+        <v>785</v>
+      </c>
+      <c r="H28" s="18">
+        <v>25</v>
+      </c>
+      <c r="I28" s="18">
+        <f>G28-H28</f>
+        <v>760</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M28" s="17"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="17"/>
+      <c r="B29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>1820</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G29" s="18">
+        <v>0</v>
+      </c>
+      <c r="H29" s="18">
+        <v>25</v>
+      </c>
+      <c r="I29" s="18">
+        <f>G29-H29</f>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17">
+        <v>1</v>
+      </c>
+      <c r="R29" s="19">
+        <f>H29</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F30" s="18">
+        <v>4</v>
+      </c>
+      <c r="G30" s="18">
+        <v>785</v>
+      </c>
+      <c r="H30" s="18">
+        <v>25</v>
+      </c>
+      <c r="I30" s="18">
+        <f>G30-H30</f>
+        <v>760</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>1826</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F31" s="18">
+        <v>1</v>
+      </c>
+      <c r="G31" s="18">
+        <v>665</v>
+      </c>
+      <c r="H31" s="18">
+        <v>25</v>
+      </c>
+      <c r="I31" s="18">
+        <f>G31-H31</f>
+        <v>640</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M31" s="17"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G32" s="18">
+        <v>960</v>
+      </c>
+      <c r="H32" s="18">
+        <v>30</v>
+      </c>
+      <c r="I32" s="18">
+        <f>G32-H32</f>
+        <v>930</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>1755</v>
+      </c>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G34" s="1">
+        <f>SUBTOTAL(9,G3:G33)</f>
+        <v>34230</v>
+      </c>
+      <c r="H34" s="1">
+        <f>SUBTOTAL(9,H3:H33)</f>
+        <v>875</v>
+      </c>
+      <c r="I34" s="1">
+        <f>SUBTOTAL(9,I3:I33)</f>
+        <v>33355</v>
+      </c>
+      <c r="J34" s="1">
+        <f>SUBTOTAL(9,J3:J33)</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <f>SUBTOTAL(9,K3:K33)</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <f>SUBTOTAL(9,L3:L33)</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <f>SUBTOTAL(9,M3:M33)</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <f>SUBTOTAL(9,N3:N33)</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <f>SUBTOTAL(9,O3:O33)</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <f>SUBTOTAL(9,P3:P33)</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
+        <f>SUBTOTAL(9,Q3:Q33)</f>
+        <v>30</v>
+      </c>
+      <c r="R34" s="1">
+        <f>SUBTOTAL(9,R3:R33)</f>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I35" s="26">
+        <f>-H49</f>
+        <v>-930</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I36" s="26"/>
+    </row>
+    <row r="38" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="4" t="s">
+        <v>1750</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="8">
+        <f>SUM(I33:I37)</f>
+        <v>32425</v>
+      </c>
+      <c r="J39" s="8">
+        <f>Q34</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="10">
+        <f>R34</f>
+        <v>185</v>
+      </c>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H41" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="10">
+        <f>S33</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="11"/>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H42" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="10">
+        <f>T33</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H43" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="10">
+        <f>U33</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="11"/>
+    </row>
+    <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H44" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H45" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H46" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="16">
+        <f>SUM(I39:I45)</f>
+        <v>32610</v>
+      </c>
+      <c r="J46" s="16">
+        <f>SUM(J39:J43)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E48" s="25">
+        <v>1</v>
+      </c>
+      <c r="F48" s="25">
+        <v>955</v>
+      </c>
+      <c r="G48" s="25">
+        <v>25</v>
+      </c>
+      <c r="H48" s="25">
+        <f>F48-G48</f>
+        <v>930</v>
+      </c>
+      <c r="I48" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J48" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K48" s="24" t="s">
+        <v>1642</v>
+      </c>
+      <c r="L48" s="24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H49" s="26">
+        <f>SUM(H48)</f>
+        <v>930</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P32" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P32">
+      <sortCondition ref="J2:J32"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
